--- a/sample_list/hcc_sample_list.xlsx
+++ b/sample_list/hcc_sample_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaylamac\Documents\Code\HCC_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaylamac\Documents\Code\HCC_2026\sample_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FEA8321-0929-4655-81C4-F6C48C6552A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB9D767-F768-44EF-A5D7-5CF8A4B08399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,7 +115,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -146,6 +146,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -159,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -189,6 +195,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -765,19 +774,19 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="11">
         <v>284</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="2"/>
@@ -29150,7 +29159,7 @@
     <col min="7" max="7" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -29270,7 +29279,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>18</v>
       </c>
@@ -29308,7 +29317,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>25</v>
       </c>
@@ -29346,7 +29355,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>26</v>
       </c>
@@ -29384,7 +29393,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>29</v>
       </c>
@@ -29422,7 +29431,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>30</v>
       </c>
@@ -29460,7 +29469,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>31</v>
       </c>
@@ -29498,7 +29507,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>33</v>
       </c>
@@ -29536,7 +29545,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>35</v>
       </c>
@@ -29574,7 +29583,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>36</v>
       </c>
@@ -29612,7 +29621,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>45</v>
       </c>
@@ -29650,7 +29659,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>48</v>
       </c>
@@ -29688,7 +29697,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>50</v>
       </c>
@@ -29726,7 +29735,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>52</v>
       </c>
@@ -29764,7 +29773,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>54</v>
       </c>
@@ -29802,7 +29811,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>56</v>
       </c>
@@ -29840,7 +29849,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>60</v>
       </c>
@@ -29878,7 +29887,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>61</v>
       </c>
@@ -29916,7 +29925,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>65</v>
       </c>
@@ -29954,7 +29963,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>70</v>
       </c>
@@ -29992,7 +30001,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -30020,7 +30029,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -30048,7 +30057,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -30076,7 +30085,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -30104,7 +30113,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -30132,7 +30141,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -30160,7 +30169,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -30188,7 +30197,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -30216,7 +30225,7 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -30244,7 +30253,7 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -30272,7 +30281,7 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -30300,7 +30309,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -30328,7 +30337,7 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -30356,7 +30365,7 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -30384,7 +30393,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -30412,7 +30421,7 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -30440,7 +30449,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -30468,7 +30477,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -30496,7 +30505,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -30524,7 +30533,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -30552,7 +30561,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -30580,7 +30589,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -30608,7 +30617,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -30636,7 +30645,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -30664,7 +30673,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -30692,7 +30701,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -30720,7 +30729,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -30748,7 +30757,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -30776,7 +30785,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -30804,7 +30813,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -30832,7 +30841,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -30860,7 +30869,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -30888,7 +30897,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -30916,7 +30925,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -30944,7 +30953,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -30972,7 +30981,7 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -31000,7 +31009,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -31028,7 +31037,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -31056,7 +31065,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -31084,7 +31093,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -31112,7 +31121,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -31140,7 +31149,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -31168,7 +31177,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -31196,7 +31205,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -31224,7 +31233,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -31252,7 +31261,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -31280,7 +31289,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -31308,7 +31317,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -31336,7 +31345,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -31364,7 +31373,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -31392,7 +31401,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -31420,7 +31429,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -31448,7 +31457,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -31476,7 +31485,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -31504,7 +31513,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -31532,7 +31541,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -31560,7 +31569,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -31588,7 +31597,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -31616,7 +31625,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -31644,7 +31653,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -31672,7 +31681,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -31700,7 +31709,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -31728,7 +31737,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -31756,7 +31765,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -31784,7 +31793,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -31812,7 +31821,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -31840,7 +31849,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -31868,7 +31877,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -31896,7 +31905,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -31924,7 +31933,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -31952,7 +31961,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -31980,7 +31989,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -32008,7 +32017,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -32036,7 +32045,7 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -32064,7 +32073,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -32092,7 +32101,7 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -32120,7 +32129,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -32148,7 +32157,7 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
     </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -32176,7 +32185,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -32204,7 +32213,7 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -32232,7 +32241,7 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -32260,7 +32269,7 @@
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -32288,7 +32297,7 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -32316,7 +32325,7 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
     </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -32344,7 +32353,7 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -32372,7 +32381,7 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
     </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -32400,7 +32409,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -32428,7 +32437,7 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -32456,7 +32465,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -32484,7 +32493,7 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
     </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -32512,7 +32521,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -32540,7 +32549,7 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
     </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -32568,7 +32577,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -32596,7 +32605,7 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
     </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -32624,7 +32633,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -32652,7 +32661,7 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
     </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -32680,7 +32689,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -32708,7 +32717,7 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
     </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -32736,7 +32745,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -32764,7 +32773,7 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
     </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -32792,7 +32801,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -32820,7 +32829,7 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
     </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -32848,7 +32857,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -32876,7 +32885,7 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
     </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -32904,7 +32913,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -32932,7 +32941,7 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
     </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -32960,7 +32969,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -32988,7 +32997,7 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
     </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -33016,7 +33025,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -33044,7 +33053,7 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
     </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -33072,7 +33081,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -33100,7 +33109,7 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
     </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -33128,7 +33137,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -33156,7 +33165,7 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
     </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -33184,7 +33193,7 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -33212,7 +33221,7 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
     </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -33240,7 +33249,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -33268,7 +33277,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
     </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -33296,7 +33305,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -33324,7 +33333,7 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
     </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -33352,7 +33361,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -33380,7 +33389,7 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
     </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -33408,7 +33417,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -33436,7 +33445,7 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -33464,7 +33473,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -33492,7 +33501,7 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -33520,7 +33529,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -33548,7 +33557,7 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
     </row>
-    <row r="150" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -33576,7 +33585,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -33604,7 +33613,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -33632,7 +33641,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -33660,7 +33669,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -33688,7 +33697,7 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -33716,7 +33725,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -33744,7 +33753,7 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -33772,7 +33781,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -33800,7 +33809,7 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -33828,7 +33837,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -33856,7 +33865,7 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
     </row>
-    <row r="161" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -33884,7 +33893,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -33912,7 +33921,7 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
     </row>
-    <row r="163" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -33940,7 +33949,7 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
     </row>
-    <row r="164" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -33968,7 +33977,7 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
     </row>
-    <row r="165" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -33996,7 +34005,7 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
     </row>
-    <row r="166" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -34024,7 +34033,7 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
     </row>
-    <row r="167" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -34052,7 +34061,7 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -34080,7 +34089,7 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
     </row>
-    <row r="169" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -34108,7 +34117,7 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -34136,7 +34145,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -34164,7 +34173,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -34192,7 +34201,7 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
     </row>
-    <row r="173" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -34220,7 +34229,7 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -34248,7 +34257,7 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -34276,7 +34285,7 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
     </row>
-    <row r="176" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -34304,7 +34313,7 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -34332,7 +34341,7 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
     </row>
-    <row r="178" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -34360,7 +34369,7 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -34388,7 +34397,7 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
     </row>
-    <row r="180" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -34416,7 +34425,7 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
     </row>
-    <row r="181" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -34444,7 +34453,7 @@
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
     </row>
-    <row r="182" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -34472,7 +34481,7 @@
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
     </row>
-    <row r="183" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -34500,7 +34509,7 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
     </row>
-    <row r="184" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -34528,7 +34537,7 @@
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
     </row>
-    <row r="185" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -34556,7 +34565,7 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
     </row>
-    <row r="186" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -34584,7 +34593,7 @@
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
     </row>
-    <row r="187" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -34612,7 +34621,7 @@
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
     </row>
-    <row r="188" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -34640,7 +34649,7 @@
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
     </row>
-    <row r="189" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -34668,7 +34677,7 @@
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
     </row>
-    <row r="190" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -34696,7 +34705,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
     </row>
-    <row r="191" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -34724,7 +34733,7 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
     </row>
-    <row r="192" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -34752,7 +34761,7 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
     </row>
-    <row r="193" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -34780,7 +34789,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
-    <row r="194" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -34808,7 +34817,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
-    <row r="195" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -34836,7 +34845,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -34864,7 +34873,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -34892,7 +34901,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -34920,7 +34929,7 @@
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
     </row>
-    <row r="199" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -34948,7 +34957,7 @@
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
     </row>
-    <row r="200" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -34976,7 +34985,7 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
     </row>
-    <row r="201" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -35004,7 +35013,7 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
     </row>
-    <row r="202" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -35032,7 +35041,7 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
     </row>
-    <row r="203" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -35060,7 +35069,7 @@
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
     </row>
-    <row r="204" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -35088,7 +35097,7 @@
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
     </row>
-    <row r="205" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -35116,7 +35125,7 @@
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
     </row>
-    <row r="206" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -35144,7 +35153,7 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
     </row>
-    <row r="207" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -35172,7 +35181,7 @@
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
     </row>
-    <row r="208" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -35200,7 +35209,7 @@
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
     </row>
-    <row r="209" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -35228,7 +35237,7 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
     </row>
-    <row r="210" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -35256,7 +35265,7 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
     </row>
-    <row r="211" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -35284,7 +35293,7 @@
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
     </row>
-    <row r="212" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -35312,7 +35321,7 @@
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
     </row>
-    <row r="213" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -35340,7 +35349,7 @@
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
     </row>
-    <row r="214" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -35368,7 +35377,7 @@
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
     </row>
-    <row r="215" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -35396,7 +35405,7 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
     </row>
-    <row r="216" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -35424,7 +35433,7 @@
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
     </row>
-    <row r="217" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -35452,7 +35461,7 @@
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
     </row>
-    <row r="218" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -35480,7 +35489,7 @@
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
     </row>
-    <row r="219" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -35508,7 +35517,7 @@
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
     </row>
-    <row r="220" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -35536,7 +35545,7 @@
       <c r="Y220" s="2"/>
       <c r="Z220" s="2"/>
     </row>
-    <row r="221" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -35564,7 +35573,7 @@
       <c r="Y221" s="2"/>
       <c r="Z221" s="2"/>
     </row>
-    <row r="222" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -35592,7 +35601,7 @@
       <c r="Y222" s="2"/>
       <c r="Z222" s="2"/>
     </row>
-    <row r="223" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -35620,7 +35629,7 @@
       <c r="Y223" s="2"/>
       <c r="Z223" s="2"/>
     </row>
-    <row r="224" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -35648,7 +35657,7 @@
       <c r="Y224" s="2"/>
       <c r="Z224" s="2"/>
     </row>
-    <row r="225" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -35676,7 +35685,7 @@
       <c r="Y225" s="2"/>
       <c r="Z225" s="2"/>
     </row>
-    <row r="226" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -35704,7 +35713,7 @@
       <c r="Y226" s="2"/>
       <c r="Z226" s="2"/>
     </row>
-    <row r="227" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -35732,7 +35741,7 @@
       <c r="Y227" s="2"/>
       <c r="Z227" s="2"/>
     </row>
-    <row r="228" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -35760,7 +35769,7 @@
       <c r="Y228" s="2"/>
       <c r="Z228" s="2"/>
     </row>
-    <row r="229" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -35788,7 +35797,7 @@
       <c r="Y229" s="2"/>
       <c r="Z229" s="2"/>
     </row>
-    <row r="230" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -35816,7 +35825,7 @@
       <c r="Y230" s="2"/>
       <c r="Z230" s="2"/>
     </row>
-    <row r="231" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -35844,7 +35853,7 @@
       <c r="Y231" s="2"/>
       <c r="Z231" s="2"/>
     </row>
-    <row r="232" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -35872,7 +35881,7 @@
       <c r="Y232" s="2"/>
       <c r="Z232" s="2"/>
     </row>
-    <row r="233" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -35900,7 +35909,7 @@
       <c r="Y233" s="2"/>
       <c r="Z233" s="2"/>
     </row>
-    <row r="234" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -35928,7 +35937,7 @@
       <c r="Y234" s="2"/>
       <c r="Z234" s="2"/>
     </row>
-    <row r="235" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -35956,7 +35965,7 @@
       <c r="Y235" s="2"/>
       <c r="Z235" s="2"/>
     </row>
-    <row r="236" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -35984,7 +35993,7 @@
       <c r="Y236" s="2"/>
       <c r="Z236" s="2"/>
     </row>
-    <row r="237" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -36012,7 +36021,7 @@
       <c r="Y237" s="2"/>
       <c r="Z237" s="2"/>
     </row>
-    <row r="238" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -36040,7 +36049,7 @@
       <c r="Y238" s="2"/>
       <c r="Z238" s="2"/>
     </row>
-    <row r="239" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -36068,7 +36077,7 @@
       <c r="Y239" s="2"/>
       <c r="Z239" s="2"/>
     </row>
-    <row r="240" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -36096,7 +36105,7 @@
       <c r="Y240" s="2"/>
       <c r="Z240" s="2"/>
     </row>
-    <row r="241" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -36124,7 +36133,7 @@
       <c r="Y241" s="2"/>
       <c r="Z241" s="2"/>
     </row>
-    <row r="242" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -36152,7 +36161,7 @@
       <c r="Y242" s="2"/>
       <c r="Z242" s="2"/>
     </row>
-    <row r="243" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -36180,7 +36189,7 @@
       <c r="Y243" s="2"/>
       <c r="Z243" s="2"/>
     </row>
-    <row r="244" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -36208,7 +36217,7 @@
       <c r="Y244" s="2"/>
       <c r="Z244" s="2"/>
     </row>
-    <row r="245" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -36236,7 +36245,7 @@
       <c r="Y245" s="2"/>
       <c r="Z245" s="2"/>
     </row>
-    <row r="246" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -36264,7 +36273,7 @@
       <c r="Y246" s="2"/>
       <c r="Z246" s="2"/>
     </row>
-    <row r="247" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -36292,7 +36301,7 @@
       <c r="Y247" s="2"/>
       <c r="Z247" s="2"/>
     </row>
-    <row r="248" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -36320,7 +36329,7 @@
       <c r="Y248" s="2"/>
       <c r="Z248" s="2"/>
     </row>
-    <row r="249" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -36348,7 +36357,7 @@
       <c r="Y249" s="2"/>
       <c r="Z249" s="2"/>
     </row>
-    <row r="250" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -36376,7 +36385,7 @@
       <c r="Y250" s="2"/>
       <c r="Z250" s="2"/>
     </row>
-    <row r="251" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -36404,7 +36413,7 @@
       <c r="Y251" s="2"/>
       <c r="Z251" s="2"/>
     </row>
-    <row r="252" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -36432,7 +36441,7 @@
       <c r="Y252" s="2"/>
       <c r="Z252" s="2"/>
     </row>
-    <row r="253" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -36460,7 +36469,7 @@
       <c r="Y253" s="2"/>
       <c r="Z253" s="2"/>
     </row>
-    <row r="254" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -36488,7 +36497,7 @@
       <c r="Y254" s="2"/>
       <c r="Z254" s="2"/>
     </row>
-    <row r="255" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -36516,7 +36525,7 @@
       <c r="Y255" s="2"/>
       <c r="Z255" s="2"/>
     </row>
-    <row r="256" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -36544,7 +36553,7 @@
       <c r="Y256" s="2"/>
       <c r="Z256" s="2"/>
     </row>
-    <row r="257" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -36572,7 +36581,7 @@
       <c r="Y257" s="2"/>
       <c r="Z257" s="2"/>
     </row>
-    <row r="258" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -36600,7 +36609,7 @@
       <c r="Y258" s="2"/>
       <c r="Z258" s="2"/>
     </row>
-    <row r="259" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -36628,7 +36637,7 @@
       <c r="Y259" s="2"/>
       <c r="Z259" s="2"/>
     </row>
-    <row r="260" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -36656,7 +36665,7 @@
       <c r="Y260" s="2"/>
       <c r="Z260" s="2"/>
     </row>
-    <row r="261" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -36684,7 +36693,7 @@
       <c r="Y261" s="2"/>
       <c r="Z261" s="2"/>
     </row>
-    <row r="262" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -36712,7 +36721,7 @@
       <c r="Y262" s="2"/>
       <c r="Z262" s="2"/>
     </row>
-    <row r="263" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -36740,7 +36749,7 @@
       <c r="Y263" s="2"/>
       <c r="Z263" s="2"/>
     </row>
-    <row r="264" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -36768,7 +36777,7 @@
       <c r="Y264" s="2"/>
       <c r="Z264" s="2"/>
     </row>
-    <row r="265" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -36796,7 +36805,7 @@
       <c r="Y265" s="2"/>
       <c r="Z265" s="2"/>
     </row>
-    <row r="266" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -36824,7 +36833,7 @@
       <c r="Y266" s="2"/>
       <c r="Z266" s="2"/>
     </row>
-    <row r="267" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -36852,7 +36861,7 @@
       <c r="Y267" s="2"/>
       <c r="Z267" s="2"/>
     </row>
-    <row r="268" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -36880,7 +36889,7 @@
       <c r="Y268" s="2"/>
       <c r="Z268" s="2"/>
     </row>
-    <row r="269" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -36908,7 +36917,7 @@
       <c r="Y269" s="2"/>
       <c r="Z269" s="2"/>
     </row>
-    <row r="270" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -36936,7 +36945,7 @@
       <c r="Y270" s="2"/>
       <c r="Z270" s="2"/>
     </row>
-    <row r="271" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -36964,7 +36973,7 @@
       <c r="Y271" s="2"/>
       <c r="Z271" s="2"/>
     </row>
-    <row r="272" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -36992,7 +37001,7 @@
       <c r="Y272" s="2"/>
       <c r="Z272" s="2"/>
     </row>
-    <row r="273" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -37020,7 +37029,7 @@
       <c r="Y273" s="2"/>
       <c r="Z273" s="2"/>
     </row>
-    <row r="274" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -37048,7 +37057,7 @@
       <c r="Y274" s="2"/>
       <c r="Z274" s="2"/>
     </row>
-    <row r="275" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -37076,7 +37085,7 @@
       <c r="Y275" s="2"/>
       <c r="Z275" s="2"/>
     </row>
-    <row r="276" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -37104,7 +37113,7 @@
       <c r="Y276" s="2"/>
       <c r="Z276" s="2"/>
     </row>
-    <row r="277" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -37132,7 +37141,7 @@
       <c r="Y277" s="2"/>
       <c r="Z277" s="2"/>
     </row>
-    <row r="278" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -37160,7 +37169,7 @@
       <c r="Y278" s="2"/>
       <c r="Z278" s="2"/>
     </row>
-    <row r="279" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -37188,7 +37197,7 @@
       <c r="Y279" s="2"/>
       <c r="Z279" s="2"/>
     </row>
-    <row r="280" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -37216,7 +37225,7 @@
       <c r="Y280" s="2"/>
       <c r="Z280" s="2"/>
     </row>
-    <row r="281" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -37244,7 +37253,7 @@
       <c r="Y281" s="2"/>
       <c r="Z281" s="2"/>
     </row>
-    <row r="282" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -37272,7 +37281,7 @@
       <c r="Y282" s="2"/>
       <c r="Z282" s="2"/>
     </row>
-    <row r="283" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -37300,7 +37309,7 @@
       <c r="Y283" s="2"/>
       <c r="Z283" s="2"/>
     </row>
-    <row r="284" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -37328,7 +37337,7 @@
       <c r="Y284" s="2"/>
       <c r="Z284" s="2"/>
     </row>
-    <row r="285" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -37356,7 +37365,7 @@
       <c r="Y285" s="2"/>
       <c r="Z285" s="2"/>
     </row>
-    <row r="286" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -37384,7 +37393,7 @@
       <c r="Y286" s="2"/>
       <c r="Z286" s="2"/>
     </row>
-    <row r="287" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -37412,7 +37421,7 @@
       <c r="Y287" s="2"/>
       <c r="Z287" s="2"/>
     </row>
-    <row r="288" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -37440,7 +37449,7 @@
       <c r="Y288" s="2"/>
       <c r="Z288" s="2"/>
     </row>
-    <row r="289" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -37468,7 +37477,7 @@
       <c r="Y289" s="2"/>
       <c r="Z289" s="2"/>
     </row>
-    <row r="290" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -37496,7 +37505,7 @@
       <c r="Y290" s="2"/>
       <c r="Z290" s="2"/>
     </row>
-    <row r="291" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -37524,7 +37533,7 @@
       <c r="Y291" s="2"/>
       <c r="Z291" s="2"/>
     </row>
-    <row r="292" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -37552,7 +37561,7 @@
       <c r="Y292" s="2"/>
       <c r="Z292" s="2"/>
     </row>
-    <row r="293" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -37580,7 +37589,7 @@
       <c r="Y293" s="2"/>
       <c r="Z293" s="2"/>
     </row>
-    <row r="294" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -37608,7 +37617,7 @@
       <c r="Y294" s="2"/>
       <c r="Z294" s="2"/>
     </row>
-    <row r="295" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -37636,7 +37645,7 @@
       <c r="Y295" s="2"/>
       <c r="Z295" s="2"/>
     </row>
-    <row r="296" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -37664,7 +37673,7 @@
       <c r="Y296" s="2"/>
       <c r="Z296" s="2"/>
     </row>
-    <row r="297" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -37692,7 +37701,7 @@
       <c r="Y297" s="2"/>
       <c r="Z297" s="2"/>
     </row>
-    <row r="298" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -37720,7 +37729,7 @@
       <c r="Y298" s="2"/>
       <c r="Z298" s="2"/>
     </row>
-    <row r="299" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -37748,7 +37757,7 @@
       <c r="Y299" s="2"/>
       <c r="Z299" s="2"/>
     </row>
-    <row r="300" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -37776,7 +37785,7 @@
       <c r="Y300" s="2"/>
       <c r="Z300" s="2"/>
     </row>
-    <row r="301" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -37804,7 +37813,7 @@
       <c r="Y301" s="2"/>
       <c r="Z301" s="2"/>
     </row>
-    <row r="302" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -37832,7 +37841,7 @@
       <c r="Y302" s="2"/>
       <c r="Z302" s="2"/>
     </row>
-    <row r="303" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -37860,7 +37869,7 @@
       <c r="Y303" s="2"/>
       <c r="Z303" s="2"/>
     </row>
-    <row r="304" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -37888,7 +37897,7 @@
       <c r="Y304" s="2"/>
       <c r="Z304" s="2"/>
     </row>
-    <row r="305" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -37916,7 +37925,7 @@
       <c r="Y305" s="2"/>
       <c r="Z305" s="2"/>
     </row>
-    <row r="306" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -37944,7 +37953,7 @@
       <c r="Y306" s="2"/>
       <c r="Z306" s="2"/>
     </row>
-    <row r="307" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -37972,7 +37981,7 @@
       <c r="Y307" s="2"/>
       <c r="Z307" s="2"/>
     </row>
-    <row r="308" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -38000,7 +38009,7 @@
       <c r="Y308" s="2"/>
       <c r="Z308" s="2"/>
     </row>
-    <row r="309" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -38028,7 +38037,7 @@
       <c r="Y309" s="2"/>
       <c r="Z309" s="2"/>
     </row>
-    <row r="310" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -38056,7 +38065,7 @@
       <c r="Y310" s="2"/>
       <c r="Z310" s="2"/>
     </row>
-    <row r="311" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -38084,7 +38093,7 @@
       <c r="Y311" s="2"/>
       <c r="Z311" s="2"/>
     </row>
-    <row r="312" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -38112,7 +38121,7 @@
       <c r="Y312" s="2"/>
       <c r="Z312" s="2"/>
     </row>
-    <row r="313" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -38140,7 +38149,7 @@
       <c r="Y313" s="2"/>
       <c r="Z313" s="2"/>
     </row>
-    <row r="314" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -38168,7 +38177,7 @@
       <c r="Y314" s="2"/>
       <c r="Z314" s="2"/>
     </row>
-    <row r="315" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -38196,7 +38205,7 @@
       <c r="Y315" s="2"/>
       <c r="Z315" s="2"/>
     </row>
-    <row r="316" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -38224,7 +38233,7 @@
       <c r="Y316" s="2"/>
       <c r="Z316" s="2"/>
     </row>
-    <row r="317" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -38252,7 +38261,7 @@
       <c r="Y317" s="2"/>
       <c r="Z317" s="2"/>
     </row>
-    <row r="318" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -38280,7 +38289,7 @@
       <c r="Y318" s="2"/>
       <c r="Z318" s="2"/>
     </row>
-    <row r="319" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -38308,7 +38317,7 @@
       <c r="Y319" s="2"/>
       <c r="Z319" s="2"/>
     </row>
-    <row r="320" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -38336,7 +38345,7 @@
       <c r="Y320" s="2"/>
       <c r="Z320" s="2"/>
     </row>
-    <row r="321" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -38364,7 +38373,7 @@
       <c r="Y321" s="2"/>
       <c r="Z321" s="2"/>
     </row>
-    <row r="322" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -38392,7 +38401,7 @@
       <c r="Y322" s="2"/>
       <c r="Z322" s="2"/>
     </row>
-    <row r="323" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -38420,7 +38429,7 @@
       <c r="Y323" s="2"/>
       <c r="Z323" s="2"/>
     </row>
-    <row r="324" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -38448,7 +38457,7 @@
       <c r="Y324" s="2"/>
       <c r="Z324" s="2"/>
     </row>
-    <row r="325" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -38476,7 +38485,7 @@
       <c r="Y325" s="2"/>
       <c r="Z325" s="2"/>
     </row>
-    <row r="326" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -38504,7 +38513,7 @@
       <c r="Y326" s="2"/>
       <c r="Z326" s="2"/>
     </row>
-    <row r="327" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -38532,7 +38541,7 @@
       <c r="Y327" s="2"/>
       <c r="Z327" s="2"/>
     </row>
-    <row r="328" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -38560,7 +38569,7 @@
       <c r="Y328" s="2"/>
       <c r="Z328" s="2"/>
     </row>
-    <row r="329" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -38588,7 +38597,7 @@
       <c r="Y329" s="2"/>
       <c r="Z329" s="2"/>
     </row>
-    <row r="330" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -38616,7 +38625,7 @@
       <c r="Y330" s="2"/>
       <c r="Z330" s="2"/>
     </row>
-    <row r="331" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -38644,7 +38653,7 @@
       <c r="Y331" s="2"/>
       <c r="Z331" s="2"/>
     </row>
-    <row r="332" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -38672,7 +38681,7 @@
       <c r="Y332" s="2"/>
       <c r="Z332" s="2"/>
     </row>
-    <row r="333" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -38700,7 +38709,7 @@
       <c r="Y333" s="2"/>
       <c r="Z333" s="2"/>
     </row>
-    <row r="334" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -38728,7 +38737,7 @@
       <c r="Y334" s="2"/>
       <c r="Z334" s="2"/>
     </row>
-    <row r="335" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -38756,7 +38765,7 @@
       <c r="Y335" s="2"/>
       <c r="Z335" s="2"/>
     </row>
-    <row r="336" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -38784,7 +38793,7 @@
       <c r="Y336" s="2"/>
       <c r="Z336" s="2"/>
     </row>
-    <row r="337" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -38812,7 +38821,7 @@
       <c r="Y337" s="2"/>
       <c r="Z337" s="2"/>
     </row>
-    <row r="338" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -38840,7 +38849,7 @@
       <c r="Y338" s="2"/>
       <c r="Z338" s="2"/>
     </row>
-    <row r="339" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -38868,7 +38877,7 @@
       <c r="Y339" s="2"/>
       <c r="Z339" s="2"/>
     </row>
-    <row r="340" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -38896,7 +38905,7 @@
       <c r="Y340" s="2"/>
       <c r="Z340" s="2"/>
     </row>
-    <row r="341" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -38924,7 +38933,7 @@
       <c r="Y341" s="2"/>
       <c r="Z341" s="2"/>
     </row>
-    <row r="342" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -38952,7 +38961,7 @@
       <c r="Y342" s="2"/>
       <c r="Z342" s="2"/>
     </row>
-    <row r="343" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -38980,7 +38989,7 @@
       <c r="Y343" s="2"/>
       <c r="Z343" s="2"/>
     </row>
-    <row r="344" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -39008,7 +39017,7 @@
       <c r="Y344" s="2"/>
       <c r="Z344" s="2"/>
     </row>
-    <row r="345" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -39036,7 +39045,7 @@
       <c r="Y345" s="2"/>
       <c r="Z345" s="2"/>
     </row>
-    <row r="346" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -39064,7 +39073,7 @@
       <c r="Y346" s="2"/>
       <c r="Z346" s="2"/>
     </row>
-    <row r="347" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -39092,7 +39101,7 @@
       <c r="Y347" s="2"/>
       <c r="Z347" s="2"/>
     </row>
-    <row r="348" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -39120,7 +39129,7 @@
       <c r="Y348" s="2"/>
       <c r="Z348" s="2"/>
     </row>
-    <row r="349" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -39148,7 +39157,7 @@
       <c r="Y349" s="2"/>
       <c r="Z349" s="2"/>
     </row>
-    <row r="350" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -39176,7 +39185,7 @@
       <c r="Y350" s="2"/>
       <c r="Z350" s="2"/>
     </row>
-    <row r="351" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -39204,7 +39213,7 @@
       <c r="Y351" s="2"/>
       <c r="Z351" s="2"/>
     </row>
-    <row r="352" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -39232,7 +39241,7 @@
       <c r="Y352" s="2"/>
       <c r="Z352" s="2"/>
     </row>
-    <row r="353" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -39260,7 +39269,7 @@
       <c r="Y353" s="2"/>
       <c r="Z353" s="2"/>
     </row>
-    <row r="354" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
@@ -39288,7 +39297,7 @@
       <c r="Y354" s="2"/>
       <c r="Z354" s="2"/>
     </row>
-    <row r="355" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -39316,7 +39325,7 @@
       <c r="Y355" s="2"/>
       <c r="Z355" s="2"/>
     </row>
-    <row r="356" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -39344,7 +39353,7 @@
       <c r="Y356" s="2"/>
       <c r="Z356" s="2"/>
     </row>
-    <row r="357" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -39372,7 +39381,7 @@
       <c r="Y357" s="2"/>
       <c r="Z357" s="2"/>
     </row>
-    <row r="358" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -39400,7 +39409,7 @@
       <c r="Y358" s="2"/>
       <c r="Z358" s="2"/>
     </row>
-    <row r="359" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -39428,7 +39437,7 @@
       <c r="Y359" s="2"/>
       <c r="Z359" s="2"/>
     </row>
-    <row r="360" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -39456,7 +39465,7 @@
       <c r="Y360" s="2"/>
       <c r="Z360" s="2"/>
     </row>
-    <row r="361" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -39484,7 +39493,7 @@
       <c r="Y361" s="2"/>
       <c r="Z361" s="2"/>
     </row>
-    <row r="362" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -39512,7 +39521,7 @@
       <c r="Y362" s="2"/>
       <c r="Z362" s="2"/>
     </row>
-    <row r="363" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -39540,7 +39549,7 @@
       <c r="Y363" s="2"/>
       <c r="Z363" s="2"/>
     </row>
-    <row r="364" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -39568,7 +39577,7 @@
       <c r="Y364" s="2"/>
       <c r="Z364" s="2"/>
     </row>
-    <row r="365" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -39596,7 +39605,7 @@
       <c r="Y365" s="2"/>
       <c r="Z365" s="2"/>
     </row>
-    <row r="366" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -39624,7 +39633,7 @@
       <c r="Y366" s="2"/>
       <c r="Z366" s="2"/>
     </row>
-    <row r="367" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -39652,7 +39661,7 @@
       <c r="Y367" s="2"/>
       <c r="Z367" s="2"/>
     </row>
-    <row r="368" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -39680,7 +39689,7 @@
       <c r="Y368" s="2"/>
       <c r="Z368" s="2"/>
     </row>
-    <row r="369" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -39708,7 +39717,7 @@
       <c r="Y369" s="2"/>
       <c r="Z369" s="2"/>
     </row>
-    <row r="370" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -39736,7 +39745,7 @@
       <c r="Y370" s="2"/>
       <c r="Z370" s="2"/>
     </row>
-    <row r="371" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -39764,7 +39773,7 @@
       <c r="Y371" s="2"/>
       <c r="Z371" s="2"/>
     </row>
-    <row r="372" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -39792,7 +39801,7 @@
       <c r="Y372" s="2"/>
       <c r="Z372" s="2"/>
     </row>
-    <row r="373" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -39820,7 +39829,7 @@
       <c r="Y373" s="2"/>
       <c r="Z373" s="2"/>
     </row>
-    <row r="374" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -39848,7 +39857,7 @@
       <c r="Y374" s="2"/>
       <c r="Z374" s="2"/>
     </row>
-    <row r="375" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -39876,7 +39885,7 @@
       <c r="Y375" s="2"/>
       <c r="Z375" s="2"/>
     </row>
-    <row r="376" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -39904,7 +39913,7 @@
       <c r="Y376" s="2"/>
       <c r="Z376" s="2"/>
     </row>
-    <row r="377" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -39932,7 +39941,7 @@
       <c r="Y377" s="2"/>
       <c r="Z377" s="2"/>
     </row>
-    <row r="378" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -39960,7 +39969,7 @@
       <c r="Y378" s="2"/>
       <c r="Z378" s="2"/>
     </row>
-    <row r="379" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -39988,7 +39997,7 @@
       <c r="Y379" s="2"/>
       <c r="Z379" s="2"/>
     </row>
-    <row r="380" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -40016,7 +40025,7 @@
       <c r="Y380" s="2"/>
       <c r="Z380" s="2"/>
     </row>
-    <row r="381" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -40044,7 +40053,7 @@
       <c r="Y381" s="2"/>
       <c r="Z381" s="2"/>
     </row>
-    <row r="382" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -40072,7 +40081,7 @@
       <c r="Y382" s="2"/>
       <c r="Z382" s="2"/>
     </row>
-    <row r="383" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -40100,7 +40109,7 @@
       <c r="Y383" s="2"/>
       <c r="Z383" s="2"/>
     </row>
-    <row r="384" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -40128,7 +40137,7 @@
       <c r="Y384" s="2"/>
       <c r="Z384" s="2"/>
     </row>
-    <row r="385" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -40156,7 +40165,7 @@
       <c r="Y385" s="2"/>
       <c r="Z385" s="2"/>
     </row>
-    <row r="386" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -40184,7 +40193,7 @@
       <c r="Y386" s="2"/>
       <c r="Z386" s="2"/>
     </row>
-    <row r="387" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -40212,7 +40221,7 @@
       <c r="Y387" s="2"/>
       <c r="Z387" s="2"/>
     </row>
-    <row r="388" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -40240,7 +40249,7 @@
       <c r="Y388" s="2"/>
       <c r="Z388" s="2"/>
     </row>
-    <row r="389" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -40268,7 +40277,7 @@
       <c r="Y389" s="2"/>
       <c r="Z389" s="2"/>
     </row>
-    <row r="390" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -40296,7 +40305,7 @@
       <c r="Y390" s="2"/>
       <c r="Z390" s="2"/>
     </row>
-    <row r="391" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -40324,7 +40333,7 @@
       <c r="Y391" s="2"/>
       <c r="Z391" s="2"/>
     </row>
-    <row r="392" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -40352,7 +40361,7 @@
       <c r="Y392" s="2"/>
       <c r="Z392" s="2"/>
     </row>
-    <row r="393" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -40380,7 +40389,7 @@
       <c r="Y393" s="2"/>
       <c r="Z393" s="2"/>
     </row>
-    <row r="394" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -40408,7 +40417,7 @@
       <c r="Y394" s="2"/>
       <c r="Z394" s="2"/>
     </row>
-    <row r="395" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -40436,7 +40445,7 @@
       <c r="Y395" s="2"/>
       <c r="Z395" s="2"/>
     </row>
-    <row r="396" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -40464,7 +40473,7 @@
       <c r="Y396" s="2"/>
       <c r="Z396" s="2"/>
     </row>
-    <row r="397" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -40492,7 +40501,7 @@
       <c r="Y397" s="2"/>
       <c r="Z397" s="2"/>
     </row>
-    <row r="398" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -40520,7 +40529,7 @@
       <c r="Y398" s="2"/>
       <c r="Z398" s="2"/>
     </row>
-    <row r="399" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -40548,7 +40557,7 @@
       <c r="Y399" s="2"/>
       <c r="Z399" s="2"/>
     </row>
-    <row r="400" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -40576,7 +40585,7 @@
       <c r="Y400" s="2"/>
       <c r="Z400" s="2"/>
     </row>
-    <row r="401" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -40604,7 +40613,7 @@
       <c r="Y401" s="2"/>
       <c r="Z401" s="2"/>
     </row>
-    <row r="402" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -40632,7 +40641,7 @@
       <c r="Y402" s="2"/>
       <c r="Z402" s="2"/>
     </row>
-    <row r="403" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -40660,7 +40669,7 @@
       <c r="Y403" s="2"/>
       <c r="Z403" s="2"/>
     </row>
-    <row r="404" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -40688,7 +40697,7 @@
       <c r="Y404" s="2"/>
       <c r="Z404" s="2"/>
     </row>
-    <row r="405" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -40716,7 +40725,7 @@
       <c r="Y405" s="2"/>
       <c r="Z405" s="2"/>
     </row>
-    <row r="406" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -40744,7 +40753,7 @@
       <c r="Y406" s="2"/>
       <c r="Z406" s="2"/>
     </row>
-    <row r="407" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
@@ -40772,7 +40781,7 @@
       <c r="Y407" s="2"/>
       <c r="Z407" s="2"/>
     </row>
-    <row r="408" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -40800,7 +40809,7 @@
       <c r="Y408" s="2"/>
       <c r="Z408" s="2"/>
     </row>
-    <row r="409" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -40828,7 +40837,7 @@
       <c r="Y409" s="2"/>
       <c r="Z409" s="2"/>
     </row>
-    <row r="410" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -40856,7 +40865,7 @@
       <c r="Y410" s="2"/>
       <c r="Z410" s="2"/>
     </row>
-    <row r="411" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -40884,7 +40893,7 @@
       <c r="Y411" s="2"/>
       <c r="Z411" s="2"/>
     </row>
-    <row r="412" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -40912,7 +40921,7 @@
       <c r="Y412" s="2"/>
       <c r="Z412" s="2"/>
     </row>
-    <row r="413" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -40940,7 +40949,7 @@
       <c r="Y413" s="2"/>
       <c r="Z413" s="2"/>
     </row>
-    <row r="414" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
@@ -40968,7 +40977,7 @@
       <c r="Y414" s="2"/>
       <c r="Z414" s="2"/>
     </row>
-    <row r="415" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -40996,7 +41005,7 @@
       <c r="Y415" s="2"/>
       <c r="Z415" s="2"/>
     </row>
-    <row r="416" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
@@ -41024,7 +41033,7 @@
       <c r="Y416" s="2"/>
       <c r="Z416" s="2"/>
     </row>
-    <row r="417" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -41052,7 +41061,7 @@
       <c r="Y417" s="2"/>
       <c r="Z417" s="2"/>
     </row>
-    <row r="418" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -41080,7 +41089,7 @@
       <c r="Y418" s="2"/>
       <c r="Z418" s="2"/>
     </row>
-    <row r="419" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -41108,7 +41117,7 @@
       <c r="Y419" s="2"/>
       <c r="Z419" s="2"/>
     </row>
-    <row r="420" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
@@ -41136,7 +41145,7 @@
       <c r="Y420" s="2"/>
       <c r="Z420" s="2"/>
     </row>
-    <row r="421" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -41164,7 +41173,7 @@
       <c r="Y421" s="2"/>
       <c r="Z421" s="2"/>
     </row>
-    <row r="422" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -41192,7 +41201,7 @@
       <c r="Y422" s="2"/>
       <c r="Z422" s="2"/>
     </row>
-    <row r="423" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -41220,7 +41229,7 @@
       <c r="Y423" s="2"/>
       <c r="Z423" s="2"/>
     </row>
-    <row r="424" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -41248,7 +41257,7 @@
       <c r="Y424" s="2"/>
       <c r="Z424" s="2"/>
     </row>
-    <row r="425" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -41276,7 +41285,7 @@
       <c r="Y425" s="2"/>
       <c r="Z425" s="2"/>
     </row>
-    <row r="426" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
@@ -41304,7 +41313,7 @@
       <c r="Y426" s="2"/>
       <c r="Z426" s="2"/>
     </row>
-    <row r="427" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -41332,7 +41341,7 @@
       <c r="Y427" s="2"/>
       <c r="Z427" s="2"/>
     </row>
-    <row r="428" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -41360,7 +41369,7 @@
       <c r="Y428" s="2"/>
       <c r="Z428" s="2"/>
     </row>
-    <row r="429" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
@@ -41388,7 +41397,7 @@
       <c r="Y429" s="2"/>
       <c r="Z429" s="2"/>
     </row>
-    <row r="430" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -41416,7 +41425,7 @@
       <c r="Y430" s="2"/>
       <c r="Z430" s="2"/>
     </row>
-    <row r="431" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -41444,7 +41453,7 @@
       <c r="Y431" s="2"/>
       <c r="Z431" s="2"/>
     </row>
-    <row r="432" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
@@ -41472,7 +41481,7 @@
       <c r="Y432" s="2"/>
       <c r="Z432" s="2"/>
     </row>
-    <row r="433" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -41500,7 +41509,7 @@
       <c r="Y433" s="2"/>
       <c r="Z433" s="2"/>
     </row>
-    <row r="434" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -41528,7 +41537,7 @@
       <c r="Y434" s="2"/>
       <c r="Z434" s="2"/>
     </row>
-    <row r="435" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -41556,7 +41565,7 @@
       <c r="Y435" s="2"/>
       <c r="Z435" s="2"/>
     </row>
-    <row r="436" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -41584,7 +41593,7 @@
       <c r="Y436" s="2"/>
       <c r="Z436" s="2"/>
     </row>
-    <row r="437" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
@@ -41612,7 +41621,7 @@
       <c r="Y437" s="2"/>
       <c r="Z437" s="2"/>
     </row>
-    <row r="438" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -41640,7 +41649,7 @@
       <c r="Y438" s="2"/>
       <c r="Z438" s="2"/>
     </row>
-    <row r="439" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -41668,7 +41677,7 @@
       <c r="Y439" s="2"/>
       <c r="Z439" s="2"/>
     </row>
-    <row r="440" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -41696,7 +41705,7 @@
       <c r="Y440" s="2"/>
       <c r="Z440" s="2"/>
     </row>
-    <row r="441" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -41724,7 +41733,7 @@
       <c r="Y441" s="2"/>
       <c r="Z441" s="2"/>
     </row>
-    <row r="442" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -41752,7 +41761,7 @@
       <c r="Y442" s="2"/>
       <c r="Z442" s="2"/>
     </row>
-    <row r="443" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
@@ -41780,7 +41789,7 @@
       <c r="Y443" s="2"/>
       <c r="Z443" s="2"/>
     </row>
-    <row r="444" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -41808,7 +41817,7 @@
       <c r="Y444" s="2"/>
       <c r="Z444" s="2"/>
     </row>
-    <row r="445" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -41836,7 +41845,7 @@
       <c r="Y445" s="2"/>
       <c r="Z445" s="2"/>
     </row>
-    <row r="446" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -41864,7 +41873,7 @@
       <c r="Y446" s="2"/>
       <c r="Z446" s="2"/>
     </row>
-    <row r="447" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -41892,7 +41901,7 @@
       <c r="Y447" s="2"/>
       <c r="Z447" s="2"/>
     </row>
-    <row r="448" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -41920,7 +41929,7 @@
       <c r="Y448" s="2"/>
       <c r="Z448" s="2"/>
     </row>
-    <row r="449" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
@@ -41948,7 +41957,7 @@
       <c r="Y449" s="2"/>
       <c r="Z449" s="2"/>
     </row>
-    <row r="450" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -41976,7 +41985,7 @@
       <c r="Y450" s="2"/>
       <c r="Z450" s="2"/>
     </row>
-    <row r="451" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -42004,7 +42013,7 @@
       <c r="Y451" s="2"/>
       <c r="Z451" s="2"/>
     </row>
-    <row r="452" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -42032,7 +42041,7 @@
       <c r="Y452" s="2"/>
       <c r="Z452" s="2"/>
     </row>
-    <row r="453" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -42060,7 +42069,7 @@
       <c r="Y453" s="2"/>
       <c r="Z453" s="2"/>
     </row>
-    <row r="454" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -42088,7 +42097,7 @@
       <c r="Y454" s="2"/>
       <c r="Z454" s="2"/>
     </row>
-    <row r="455" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
@@ -42116,7 +42125,7 @@
       <c r="Y455" s="2"/>
       <c r="Z455" s="2"/>
     </row>
-    <row r="456" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -42144,7 +42153,7 @@
       <c r="Y456" s="2"/>
       <c r="Z456" s="2"/>
     </row>
-    <row r="457" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -42172,7 +42181,7 @@
       <c r="Y457" s="2"/>
       <c r="Z457" s="2"/>
     </row>
-    <row r="458" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -42200,7 +42209,7 @@
       <c r="Y458" s="2"/>
       <c r="Z458" s="2"/>
     </row>
-    <row r="459" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -42228,7 +42237,7 @@
       <c r="Y459" s="2"/>
       <c r="Z459" s="2"/>
     </row>
-    <row r="460" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -42256,7 +42265,7 @@
       <c r="Y460" s="2"/>
       <c r="Z460" s="2"/>
     </row>
-    <row r="461" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
@@ -42284,7 +42293,7 @@
       <c r="Y461" s="2"/>
       <c r="Z461" s="2"/>
     </row>
-    <row r="462" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -42312,7 +42321,7 @@
       <c r="Y462" s="2"/>
       <c r="Z462" s="2"/>
     </row>
-    <row r="463" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -42340,7 +42349,7 @@
       <c r="Y463" s="2"/>
       <c r="Z463" s="2"/>
     </row>
-    <row r="464" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
@@ -42368,7 +42377,7 @@
       <c r="Y464" s="2"/>
       <c r="Z464" s="2"/>
     </row>
-    <row r="465" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -42396,7 +42405,7 @@
       <c r="Y465" s="2"/>
       <c r="Z465" s="2"/>
     </row>
-    <row r="466" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
@@ -42424,7 +42433,7 @@
       <c r="Y466" s="2"/>
       <c r="Z466" s="2"/>
     </row>
-    <row r="467" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -42452,7 +42461,7 @@
       <c r="Y467" s="2"/>
       <c r="Z467" s="2"/>
     </row>
-    <row r="468" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
@@ -42480,7 +42489,7 @@
       <c r="Y468" s="2"/>
       <c r="Z468" s="2"/>
     </row>
-    <row r="469" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -42508,7 +42517,7 @@
       <c r="Y469" s="2"/>
       <c r="Z469" s="2"/>
     </row>
-    <row r="470" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
@@ -42536,7 +42545,7 @@
       <c r="Y470" s="2"/>
       <c r="Z470" s="2"/>
     </row>
-    <row r="471" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -42564,7 +42573,7 @@
       <c r="Y471" s="2"/>
       <c r="Z471" s="2"/>
     </row>
-    <row r="472" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -42592,7 +42601,7 @@
       <c r="Y472" s="2"/>
       <c r="Z472" s="2"/>
     </row>
-    <row r="473" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
@@ -42620,7 +42629,7 @@
       <c r="Y473" s="2"/>
       <c r="Z473" s="2"/>
     </row>
-    <row r="474" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -42648,7 +42657,7 @@
       <c r="Y474" s="2"/>
       <c r="Z474" s="2"/>
     </row>
-    <row r="475" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -42676,7 +42685,7 @@
       <c r="Y475" s="2"/>
       <c r="Z475" s="2"/>
     </row>
-    <row r="476" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -42704,7 +42713,7 @@
       <c r="Y476" s="2"/>
       <c r="Z476" s="2"/>
     </row>
-    <row r="477" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -42732,7 +42741,7 @@
       <c r="Y477" s="2"/>
       <c r="Z477" s="2"/>
     </row>
-    <row r="478" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -42760,7 +42769,7 @@
       <c r="Y478" s="2"/>
       <c r="Z478" s="2"/>
     </row>
-    <row r="479" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -42788,7 +42797,7 @@
       <c r="Y479" s="2"/>
       <c r="Z479" s="2"/>
     </row>
-    <row r="480" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -42816,7 +42825,7 @@
       <c r="Y480" s="2"/>
       <c r="Z480" s="2"/>
     </row>
-    <row r="481" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -42844,7 +42853,7 @@
       <c r="Y481" s="2"/>
       <c r="Z481" s="2"/>
     </row>
-    <row r="482" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
@@ -42872,7 +42881,7 @@
       <c r="Y482" s="2"/>
       <c r="Z482" s="2"/>
     </row>
-    <row r="483" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -42900,7 +42909,7 @@
       <c r="Y483" s="2"/>
       <c r="Z483" s="2"/>
     </row>
-    <row r="484" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -42928,7 +42937,7 @@
       <c r="Y484" s="2"/>
       <c r="Z484" s="2"/>
     </row>
-    <row r="485" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -42956,7 +42965,7 @@
       <c r="Y485" s="2"/>
       <c r="Z485" s="2"/>
     </row>
-    <row r="486" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -42984,7 +42993,7 @@
       <c r="Y486" s="2"/>
       <c r="Z486" s="2"/>
     </row>
-    <row r="487" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -43012,7 +43021,7 @@
       <c r="Y487" s="2"/>
       <c r="Z487" s="2"/>
     </row>
-    <row r="488" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
@@ -43040,7 +43049,7 @@
       <c r="Y488" s="2"/>
       <c r="Z488" s="2"/>
     </row>
-    <row r="489" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -43068,7 +43077,7 @@
       <c r="Y489" s="2"/>
       <c r="Z489" s="2"/>
     </row>
-    <row r="490" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -43096,7 +43105,7 @@
       <c r="Y490" s="2"/>
       <c r="Z490" s="2"/>
     </row>
-    <row r="491" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -43124,7 +43133,7 @@
       <c r="Y491" s="2"/>
       <c r="Z491" s="2"/>
     </row>
-    <row r="492" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -43152,7 +43161,7 @@
       <c r="Y492" s="2"/>
       <c r="Z492" s="2"/>
     </row>
-    <row r="493" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -43180,7 +43189,7 @@
       <c r="Y493" s="2"/>
       <c r="Z493" s="2"/>
     </row>
-    <row r="494" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
@@ -43208,7 +43217,7 @@
       <c r="Y494" s="2"/>
       <c r="Z494" s="2"/>
     </row>
-    <row r="495" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -43236,7 +43245,7 @@
       <c r="Y495" s="2"/>
       <c r="Z495" s="2"/>
     </row>
-    <row r="496" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -43264,7 +43273,7 @@
       <c r="Y496" s="2"/>
       <c r="Z496" s="2"/>
     </row>
-    <row r="497" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -43292,7 +43301,7 @@
       <c r="Y497" s="2"/>
       <c r="Z497" s="2"/>
     </row>
-    <row r="498" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -43320,7 +43329,7 @@
       <c r="Y498" s="2"/>
       <c r="Z498" s="2"/>
     </row>
-    <row r="499" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -43348,7 +43357,7 @@
       <c r="Y499" s="2"/>
       <c r="Z499" s="2"/>
     </row>
-    <row r="500" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -43376,7 +43385,7 @@
       <c r="Y500" s="2"/>
       <c r="Z500" s="2"/>
     </row>
-    <row r="501" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="2"/>
@@ -43404,7 +43413,7 @@
       <c r="Y501" s="2"/>
       <c r="Z501" s="2"/>
     </row>
-    <row r="502" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -43432,7 +43441,7 @@
       <c r="Y502" s="2"/>
       <c r="Z502" s="2"/>
     </row>
-    <row r="503" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="2"/>
@@ -43460,7 +43469,7 @@
       <c r="Y503" s="2"/>
       <c r="Z503" s="2"/>
     </row>
-    <row r="504" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="2"/>
@@ -43488,7 +43497,7 @@
       <c r="Y504" s="2"/>
       <c r="Z504" s="2"/>
     </row>
-    <row r="505" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="2"/>
@@ -43516,7 +43525,7 @@
       <c r="Y505" s="2"/>
       <c r="Z505" s="2"/>
     </row>
-    <row r="506" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="2"/>
@@ -43544,7 +43553,7 @@
       <c r="Y506" s="2"/>
       <c r="Z506" s="2"/>
     </row>
-    <row r="507" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="2"/>
@@ -43572,7 +43581,7 @@
       <c r="Y507" s="2"/>
       <c r="Z507" s="2"/>
     </row>
-    <row r="508" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
@@ -43600,7 +43609,7 @@
       <c r="Y508" s="2"/>
       <c r="Z508" s="2"/>
     </row>
-    <row r="509" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="2"/>
@@ -43628,7 +43637,7 @@
       <c r="Y509" s="2"/>
       <c r="Z509" s="2"/>
     </row>
-    <row r="510" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="2"/>
@@ -43656,7 +43665,7 @@
       <c r="Y510" s="2"/>
       <c r="Z510" s="2"/>
     </row>
-    <row r="511" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="2"/>
@@ -43684,7 +43693,7 @@
       <c r="Y511" s="2"/>
       <c r="Z511" s="2"/>
     </row>
-    <row r="512" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="2"/>
@@ -43712,7 +43721,7 @@
       <c r="Y512" s="2"/>
       <c r="Z512" s="2"/>
     </row>
-    <row r="513" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="2"/>
@@ -43740,7 +43749,7 @@
       <c r="Y513" s="2"/>
       <c r="Z513" s="2"/>
     </row>
-    <row r="514" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="2"/>
@@ -43768,7 +43777,7 @@
       <c r="Y514" s="2"/>
       <c r="Z514" s="2"/>
     </row>
-    <row r="515" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
@@ -43796,7 +43805,7 @@
       <c r="Y515" s="2"/>
       <c r="Z515" s="2"/>
     </row>
-    <row r="516" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
@@ -43824,7 +43833,7 @@
       <c r="Y516" s="2"/>
       <c r="Z516" s="2"/>
     </row>
-    <row r="517" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
@@ -43852,7 +43861,7 @@
       <c r="Y517" s="2"/>
       <c r="Z517" s="2"/>
     </row>
-    <row r="518" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="2"/>
@@ -43880,7 +43889,7 @@
       <c r="Y518" s="2"/>
       <c r="Z518" s="2"/>
     </row>
-    <row r="519" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
@@ -43908,7 +43917,7 @@
       <c r="Y519" s="2"/>
       <c r="Z519" s="2"/>
     </row>
-    <row r="520" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
@@ -43936,7 +43945,7 @@
       <c r="Y520" s="2"/>
       <c r="Z520" s="2"/>
     </row>
-    <row r="521" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
@@ -43964,7 +43973,7 @@
       <c r="Y521" s="2"/>
       <c r="Z521" s="2"/>
     </row>
-    <row r="522" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="2"/>
@@ -43992,7 +44001,7 @@
       <c r="Y522" s="2"/>
       <c r="Z522" s="2"/>
     </row>
-    <row r="523" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
@@ -44020,7 +44029,7 @@
       <c r="Y523" s="2"/>
       <c r="Z523" s="2"/>
     </row>
-    <row r="524" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="2"/>
@@ -44048,7 +44057,7 @@
       <c r="Y524" s="2"/>
       <c r="Z524" s="2"/>
     </row>
-    <row r="525" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
@@ -44076,7 +44085,7 @@
       <c r="Y525" s="2"/>
       <c r="Z525" s="2"/>
     </row>
-    <row r="526" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="2"/>
@@ -44104,7 +44113,7 @@
       <c r="Y526" s="2"/>
       <c r="Z526" s="2"/>
     </row>
-    <row r="527" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="2"/>
@@ -44132,7 +44141,7 @@
       <c r="Y527" s="2"/>
       <c r="Z527" s="2"/>
     </row>
-    <row r="528" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="2"/>
@@ -44160,7 +44169,7 @@
       <c r="Y528" s="2"/>
       <c r="Z528" s="2"/>
     </row>
-    <row r="529" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="2"/>
@@ -44188,7 +44197,7 @@
       <c r="Y529" s="2"/>
       <c r="Z529" s="2"/>
     </row>
-    <row r="530" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="2"/>
@@ -44216,7 +44225,7 @@
       <c r="Y530" s="2"/>
       <c r="Z530" s="2"/>
     </row>
-    <row r="531" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
@@ -44244,7 +44253,7 @@
       <c r="Y531" s="2"/>
       <c r="Z531" s="2"/>
     </row>
-    <row r="532" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
@@ -44272,7 +44281,7 @@
       <c r="Y532" s="2"/>
       <c r="Z532" s="2"/>
     </row>
-    <row r="533" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
@@ -44300,7 +44309,7 @@
       <c r="Y533" s="2"/>
       <c r="Z533" s="2"/>
     </row>
-    <row r="534" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="2"/>
@@ -44328,7 +44337,7 @@
       <c r="Y534" s="2"/>
       <c r="Z534" s="2"/>
     </row>
-    <row r="535" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
@@ -44356,7 +44365,7 @@
       <c r="Y535" s="2"/>
       <c r="Z535" s="2"/>
     </row>
-    <row r="536" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
@@ -44384,7 +44393,7 @@
       <c r="Y536" s="2"/>
       <c r="Z536" s="2"/>
     </row>
-    <row r="537" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
@@ -44412,7 +44421,7 @@
       <c r="Y537" s="2"/>
       <c r="Z537" s="2"/>
     </row>
-    <row r="538" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="2"/>
@@ -44440,7 +44449,7 @@
       <c r="Y538" s="2"/>
       <c r="Z538" s="2"/>
     </row>
-    <row r="539" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="2"/>
@@ -44468,7 +44477,7 @@
       <c r="Y539" s="2"/>
       <c r="Z539" s="2"/>
     </row>
-    <row r="540" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="2"/>
@@ -44496,7 +44505,7 @@
       <c r="Y540" s="2"/>
       <c r="Z540" s="2"/>
     </row>
-    <row r="541" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="2"/>
@@ -44524,7 +44533,7 @@
       <c r="Y541" s="2"/>
       <c r="Z541" s="2"/>
     </row>
-    <row r="542" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="2"/>
@@ -44552,7 +44561,7 @@
       <c r="Y542" s="2"/>
       <c r="Z542" s="2"/>
     </row>
-    <row r="543" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
@@ -44580,7 +44589,7 @@
       <c r="Y543" s="2"/>
       <c r="Z543" s="2"/>
     </row>
-    <row r="544" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="2"/>
@@ -44608,7 +44617,7 @@
       <c r="Y544" s="2"/>
       <c r="Z544" s="2"/>
     </row>
-    <row r="545" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
@@ -44636,7 +44645,7 @@
       <c r="Y545" s="2"/>
       <c r="Z545" s="2"/>
     </row>
-    <row r="546" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
@@ -44664,7 +44673,7 @@
       <c r="Y546" s="2"/>
       <c r="Z546" s="2"/>
     </row>
-    <row r="547" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="2"/>
@@ -44692,7 +44701,7 @@
       <c r="Y547" s="2"/>
       <c r="Z547" s="2"/>
     </row>
-    <row r="548" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="2"/>
@@ -44720,7 +44729,7 @@
       <c r="Y548" s="2"/>
       <c r="Z548" s="2"/>
     </row>
-    <row r="549" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="2"/>
@@ -44748,7 +44757,7 @@
       <c r="Y549" s="2"/>
       <c r="Z549" s="2"/>
     </row>
-    <row r="550" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
@@ -44776,7 +44785,7 @@
       <c r="Y550" s="2"/>
       <c r="Z550" s="2"/>
     </row>
-    <row r="551" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="2"/>
@@ -44804,7 +44813,7 @@
       <c r="Y551" s="2"/>
       <c r="Z551" s="2"/>
     </row>
-    <row r="552" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="2"/>
@@ -44832,7 +44841,7 @@
       <c r="Y552" s="2"/>
       <c r="Z552" s="2"/>
     </row>
-    <row r="553" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="2"/>
@@ -44860,7 +44869,7 @@
       <c r="Y553" s="2"/>
       <c r="Z553" s="2"/>
     </row>
-    <row r="554" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="2"/>
@@ -44888,7 +44897,7 @@
       <c r="Y554" s="2"/>
       <c r="Z554" s="2"/>
     </row>
-    <row r="555" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="2"/>
@@ -44916,7 +44925,7 @@
       <c r="Y555" s="2"/>
       <c r="Z555" s="2"/>
     </row>
-    <row r="556" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="2"/>
@@ -44944,7 +44953,7 @@
       <c r="Y556" s="2"/>
       <c r="Z556" s="2"/>
     </row>
-    <row r="557" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
@@ -44972,7 +44981,7 @@
       <c r="Y557" s="2"/>
       <c r="Z557" s="2"/>
     </row>
-    <row r="558" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="2"/>
@@ -45000,7 +45009,7 @@
       <c r="Y558" s="2"/>
       <c r="Z558" s="2"/>
     </row>
-    <row r="559" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="2"/>
@@ -45028,7 +45037,7 @@
       <c r="Y559" s="2"/>
       <c r="Z559" s="2"/>
     </row>
-    <row r="560" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="2"/>
@@ -45056,7 +45065,7 @@
       <c r="Y560" s="2"/>
       <c r="Z560" s="2"/>
     </row>
-    <row r="561" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="2"/>
@@ -45084,7 +45093,7 @@
       <c r="Y561" s="2"/>
       <c r="Z561" s="2"/>
     </row>
-    <row r="562" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="2"/>
@@ -45112,7 +45121,7 @@
       <c r="Y562" s="2"/>
       <c r="Z562" s="2"/>
     </row>
-    <row r="563" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="2"/>
@@ -45140,7 +45149,7 @@
       <c r="Y563" s="2"/>
       <c r="Z563" s="2"/>
     </row>
-    <row r="564" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="2"/>
@@ -45168,7 +45177,7 @@
       <c r="Y564" s="2"/>
       <c r="Z564" s="2"/>
     </row>
-    <row r="565" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="2"/>
@@ -45196,7 +45205,7 @@
       <c r="Y565" s="2"/>
       <c r="Z565" s="2"/>
     </row>
-    <row r="566" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="2"/>
@@ -45224,7 +45233,7 @@
       <c r="Y566" s="2"/>
       <c r="Z566" s="2"/>
     </row>
-    <row r="567" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="2"/>
@@ -45252,7 +45261,7 @@
       <c r="Y567" s="2"/>
       <c r="Z567" s="2"/>
     </row>
-    <row r="568" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="2"/>
@@ -45280,7 +45289,7 @@
       <c r="Y568" s="2"/>
       <c r="Z568" s="2"/>
     </row>
-    <row r="569" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="2"/>
@@ -45308,7 +45317,7 @@
       <c r="Y569" s="2"/>
       <c r="Z569" s="2"/>
     </row>
-    <row r="570" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="2"/>
@@ -45336,7 +45345,7 @@
       <c r="Y570" s="2"/>
       <c r="Z570" s="2"/>
     </row>
-    <row r="571" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="2"/>
@@ -45364,7 +45373,7 @@
       <c r="Y571" s="2"/>
       <c r="Z571" s="2"/>
     </row>
-    <row r="572" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="2"/>
@@ -45392,7 +45401,7 @@
       <c r="Y572" s="2"/>
       <c r="Z572" s="2"/>
     </row>
-    <row r="573" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="2"/>
@@ -45420,7 +45429,7 @@
       <c r="Y573" s="2"/>
       <c r="Z573" s="2"/>
     </row>
-    <row r="574" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
@@ -45448,7 +45457,7 @@
       <c r="Y574" s="2"/>
       <c r="Z574" s="2"/>
     </row>
-    <row r="575" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="2"/>
@@ -45476,7 +45485,7 @@
       <c r="Y575" s="2"/>
       <c r="Z575" s="2"/>
     </row>
-    <row r="576" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="2"/>
@@ -45504,7 +45513,7 @@
       <c r="Y576" s="2"/>
       <c r="Z576" s="2"/>
     </row>
-    <row r="577" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
@@ -45532,7 +45541,7 @@
       <c r="Y577" s="2"/>
       <c r="Z577" s="2"/>
     </row>
-    <row r="578" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="2"/>
@@ -45560,7 +45569,7 @@
       <c r="Y578" s="2"/>
       <c r="Z578" s="2"/>
     </row>
-    <row r="579" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="2"/>
@@ -45588,7 +45597,7 @@
       <c r="Y579" s="2"/>
       <c r="Z579" s="2"/>
     </row>
-    <row r="580" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="2"/>
@@ -45616,7 +45625,7 @@
       <c r="Y580" s="2"/>
       <c r="Z580" s="2"/>
     </row>
-    <row r="581" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
@@ -45644,7 +45653,7 @@
       <c r="Y581" s="2"/>
       <c r="Z581" s="2"/>
     </row>
-    <row r="582" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="2"/>
@@ -45672,7 +45681,7 @@
       <c r="Y582" s="2"/>
       <c r="Z582" s="2"/>
     </row>
-    <row r="583" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
@@ -45700,7 +45709,7 @@
       <c r="Y583" s="2"/>
       <c r="Z583" s="2"/>
     </row>
-    <row r="584" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="2"/>
@@ -45728,7 +45737,7 @@
       <c r="Y584" s="2"/>
       <c r="Z584" s="2"/>
     </row>
-    <row r="585" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="2"/>
@@ -45756,7 +45765,7 @@
       <c r="Y585" s="2"/>
       <c r="Z585" s="2"/>
     </row>
-    <row r="586" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="2"/>
@@ -45784,7 +45793,7 @@
       <c r="Y586" s="2"/>
       <c r="Z586" s="2"/>
     </row>
-    <row r="587" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
@@ -45812,7 +45821,7 @@
       <c r="Y587" s="2"/>
       <c r="Z587" s="2"/>
     </row>
-    <row r="588" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="2"/>
@@ -45840,7 +45849,7 @@
       <c r="Y588" s="2"/>
       <c r="Z588" s="2"/>
     </row>
-    <row r="589" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="2"/>
@@ -45868,7 +45877,7 @@
       <c r="Y589" s="2"/>
       <c r="Z589" s="2"/>
     </row>
-    <row r="590" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="2"/>
@@ -45896,7 +45905,7 @@
       <c r="Y590" s="2"/>
       <c r="Z590" s="2"/>
     </row>
-    <row r="591" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="2"/>
@@ -45924,7 +45933,7 @@
       <c r="Y591" s="2"/>
       <c r="Z591" s="2"/>
     </row>
-    <row r="592" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="2"/>
@@ -45952,7 +45961,7 @@
       <c r="Y592" s="2"/>
       <c r="Z592" s="2"/>
     </row>
-    <row r="593" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="2"/>
@@ -45980,7 +45989,7 @@
       <c r="Y593" s="2"/>
       <c r="Z593" s="2"/>
     </row>
-    <row r="594" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="2"/>
@@ -46008,7 +46017,7 @@
       <c r="Y594" s="2"/>
       <c r="Z594" s="2"/>
     </row>
-    <row r="595" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
@@ -46036,7 +46045,7 @@
       <c r="Y595" s="2"/>
       <c r="Z595" s="2"/>
     </row>
-    <row r="596" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
@@ -46064,7 +46073,7 @@
       <c r="Y596" s="2"/>
       <c r="Z596" s="2"/>
     </row>
-    <row r="597" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="2"/>
@@ -46092,7 +46101,7 @@
       <c r="Y597" s="2"/>
       <c r="Z597" s="2"/>
     </row>
-    <row r="598" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="2"/>
@@ -46120,7 +46129,7 @@
       <c r="Y598" s="2"/>
       <c r="Z598" s="2"/>
     </row>
-    <row r="599" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="2"/>
@@ -46148,7 +46157,7 @@
       <c r="Y599" s="2"/>
       <c r="Z599" s="2"/>
     </row>
-    <row r="600" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="2"/>
@@ -46176,7 +46185,7 @@
       <c r="Y600" s="2"/>
       <c r="Z600" s="2"/>
     </row>
-    <row r="601" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="2"/>
@@ -46204,7 +46213,7 @@
       <c r="Y601" s="2"/>
       <c r="Z601" s="2"/>
     </row>
-    <row r="602" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="2"/>
@@ -46232,7 +46241,7 @@
       <c r="Y602" s="2"/>
       <c r="Z602" s="2"/>
     </row>
-    <row r="603" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="2"/>
@@ -46260,7 +46269,7 @@
       <c r="Y603" s="2"/>
       <c r="Z603" s="2"/>
     </row>
-    <row r="604" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="2"/>
@@ -46288,7 +46297,7 @@
       <c r="Y604" s="2"/>
       <c r="Z604" s="2"/>
     </row>
-    <row r="605" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="2"/>
@@ -46316,7 +46325,7 @@
       <c r="Y605" s="2"/>
       <c r="Z605" s="2"/>
     </row>
-    <row r="606" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="2"/>
@@ -46344,7 +46353,7 @@
       <c r="Y606" s="2"/>
       <c r="Z606" s="2"/>
     </row>
-    <row r="607" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="2"/>
@@ -46372,7 +46381,7 @@
       <c r="Y607" s="2"/>
       <c r="Z607" s="2"/>
     </row>
-    <row r="608" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="2"/>
@@ -46400,7 +46409,7 @@
       <c r="Y608" s="2"/>
       <c r="Z608" s="2"/>
     </row>
-    <row r="609" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="2"/>
@@ -46428,7 +46437,7 @@
       <c r="Y609" s="2"/>
       <c r="Z609" s="2"/>
     </row>
-    <row r="610" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="2"/>
@@ -46456,7 +46465,7 @@
       <c r="Y610" s="2"/>
       <c r="Z610" s="2"/>
     </row>
-    <row r="611" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="2"/>
@@ -46484,7 +46493,7 @@
       <c r="Y611" s="2"/>
       <c r="Z611" s="2"/>
     </row>
-    <row r="612" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="2"/>
@@ -46512,7 +46521,7 @@
       <c r="Y612" s="2"/>
       <c r="Z612" s="2"/>
     </row>
-    <row r="613" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="2"/>
@@ -46540,7 +46549,7 @@
       <c r="Y613" s="2"/>
       <c r="Z613" s="2"/>
     </row>
-    <row r="614" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="2"/>
@@ -46568,7 +46577,7 @@
       <c r="Y614" s="2"/>
       <c r="Z614" s="2"/>
     </row>
-    <row r="615" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="2"/>
@@ -46596,7 +46605,7 @@
       <c r="Y615" s="2"/>
       <c r="Z615" s="2"/>
     </row>
-    <row r="616" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="2"/>
@@ -46624,7 +46633,7 @@
       <c r="Y616" s="2"/>
       <c r="Z616" s="2"/>
     </row>
-    <row r="617" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="2"/>
@@ -46652,7 +46661,7 @@
       <c r="Y617" s="2"/>
       <c r="Z617" s="2"/>
     </row>
-    <row r="618" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="2"/>
@@ -46680,7 +46689,7 @@
       <c r="Y618" s="2"/>
       <c r="Z618" s="2"/>
     </row>
-    <row r="619" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="2"/>
@@ -46708,7 +46717,7 @@
       <c r="Y619" s="2"/>
       <c r="Z619" s="2"/>
     </row>
-    <row r="620" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="2"/>
@@ -46736,7 +46745,7 @@
       <c r="Y620" s="2"/>
       <c r="Z620" s="2"/>
     </row>
-    <row r="621" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="2"/>
@@ -46764,7 +46773,7 @@
       <c r="Y621" s="2"/>
       <c r="Z621" s="2"/>
     </row>
-    <row r="622" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="2"/>
@@ -46792,7 +46801,7 @@
       <c r="Y622" s="2"/>
       <c r="Z622" s="2"/>
     </row>
-    <row r="623" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="2"/>
@@ -46820,7 +46829,7 @@
       <c r="Y623" s="2"/>
       <c r="Z623" s="2"/>
     </row>
-    <row r="624" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="2"/>
@@ -46848,7 +46857,7 @@
       <c r="Y624" s="2"/>
       <c r="Z624" s="2"/>
     </row>
-    <row r="625" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="2"/>
@@ -46876,7 +46885,7 @@
       <c r="Y625" s="2"/>
       <c r="Z625" s="2"/>
     </row>
-    <row r="626" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="2"/>
@@ -46904,7 +46913,7 @@
       <c r="Y626" s="2"/>
       <c r="Z626" s="2"/>
     </row>
-    <row r="627" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
@@ -46932,7 +46941,7 @@
       <c r="Y627" s="2"/>
       <c r="Z627" s="2"/>
     </row>
-    <row r="628" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="2"/>
@@ -46960,7 +46969,7 @@
       <c r="Y628" s="2"/>
       <c r="Z628" s="2"/>
     </row>
-    <row r="629" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="2"/>
@@ -46988,7 +46997,7 @@
       <c r="Y629" s="2"/>
       <c r="Z629" s="2"/>
     </row>
-    <row r="630" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="2"/>
@@ -47016,7 +47025,7 @@
       <c r="Y630" s="2"/>
       <c r="Z630" s="2"/>
     </row>
-    <row r="631" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="2"/>
@@ -47044,7 +47053,7 @@
       <c r="Y631" s="2"/>
       <c r="Z631" s="2"/>
     </row>
-    <row r="632" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="2"/>
@@ -47072,7 +47081,7 @@
       <c r="Y632" s="2"/>
       <c r="Z632" s="2"/>
     </row>
-    <row r="633" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="2"/>
@@ -47100,7 +47109,7 @@
       <c r="Y633" s="2"/>
       <c r="Z633" s="2"/>
     </row>
-    <row r="634" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="2"/>
@@ -47128,7 +47137,7 @@
       <c r="Y634" s="2"/>
       <c r="Z634" s="2"/>
     </row>
-    <row r="635" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="2"/>
@@ -47156,7 +47165,7 @@
       <c r="Y635" s="2"/>
       <c r="Z635" s="2"/>
     </row>
-    <row r="636" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="2"/>
@@ -47184,7 +47193,7 @@
       <c r="Y636" s="2"/>
       <c r="Z636" s="2"/>
     </row>
-    <row r="637" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="2"/>
@@ -47212,7 +47221,7 @@
       <c r="Y637" s="2"/>
       <c r="Z637" s="2"/>
     </row>
-    <row r="638" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="2"/>
@@ -47240,7 +47249,7 @@
       <c r="Y638" s="2"/>
       <c r="Z638" s="2"/>
     </row>
-    <row r="639" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="2"/>
@@ -47268,7 +47277,7 @@
       <c r="Y639" s="2"/>
       <c r="Z639" s="2"/>
     </row>
-    <row r="640" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="2"/>
@@ -47296,7 +47305,7 @@
       <c r="Y640" s="2"/>
       <c r="Z640" s="2"/>
     </row>
-    <row r="641" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="2"/>
@@ -47324,7 +47333,7 @@
       <c r="Y641" s="2"/>
       <c r="Z641" s="2"/>
     </row>
-    <row r="642" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="2"/>
@@ -47352,7 +47361,7 @@
       <c r="Y642" s="2"/>
       <c r="Z642" s="2"/>
     </row>
-    <row r="643" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="2"/>
@@ -47380,7 +47389,7 @@
       <c r="Y643" s="2"/>
       <c r="Z643" s="2"/>
     </row>
-    <row r="644" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="2"/>
@@ -47408,7 +47417,7 @@
       <c r="Y644" s="2"/>
       <c r="Z644" s="2"/>
     </row>
-    <row r="645" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="2"/>
@@ -47436,7 +47445,7 @@
       <c r="Y645" s="2"/>
       <c r="Z645" s="2"/>
     </row>
-    <row r="646" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="2"/>
@@ -47464,7 +47473,7 @@
       <c r="Y646" s="2"/>
       <c r="Z646" s="2"/>
     </row>
-    <row r="647" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="2"/>
@@ -47492,7 +47501,7 @@
       <c r="Y647" s="2"/>
       <c r="Z647" s="2"/>
     </row>
-    <row r="648" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="2"/>
@@ -47520,7 +47529,7 @@
       <c r="Y648" s="2"/>
       <c r="Z648" s="2"/>
     </row>
-    <row r="649" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="2"/>
@@ -47548,7 +47557,7 @@
       <c r="Y649" s="2"/>
       <c r="Z649" s="2"/>
     </row>
-    <row r="650" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="2"/>
@@ -47576,7 +47585,7 @@
       <c r="Y650" s="2"/>
       <c r="Z650" s="2"/>
     </row>
-    <row r="651" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="2"/>
@@ -47604,7 +47613,7 @@
       <c r="Y651" s="2"/>
       <c r="Z651" s="2"/>
     </row>
-    <row r="652" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="2"/>
@@ -47632,7 +47641,7 @@
       <c r="Y652" s="2"/>
       <c r="Z652" s="2"/>
     </row>
-    <row r="653" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="2"/>
@@ -47660,7 +47669,7 @@
       <c r="Y653" s="2"/>
       <c r="Z653" s="2"/>
     </row>
-    <row r="654" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="2"/>
@@ -47688,7 +47697,7 @@
       <c r="Y654" s="2"/>
       <c r="Z654" s="2"/>
     </row>
-    <row r="655" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="2"/>
@@ -47716,7 +47725,7 @@
       <c r="Y655" s="2"/>
       <c r="Z655" s="2"/>
     </row>
-    <row r="656" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="2"/>
@@ -47744,7 +47753,7 @@
       <c r="Y656" s="2"/>
       <c r="Z656" s="2"/>
     </row>
-    <row r="657" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="2"/>
@@ -47772,7 +47781,7 @@
       <c r="Y657" s="2"/>
       <c r="Z657" s="2"/>
     </row>
-    <row r="658" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="2"/>
@@ -47800,7 +47809,7 @@
       <c r="Y658" s="2"/>
       <c r="Z658" s="2"/>
     </row>
-    <row r="659" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="2"/>
@@ -47828,7 +47837,7 @@
       <c r="Y659" s="2"/>
       <c r="Z659" s="2"/>
     </row>
-    <row r="660" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="2"/>
@@ -47856,7 +47865,7 @@
       <c r="Y660" s="2"/>
       <c r="Z660" s="2"/>
     </row>
-    <row r="661" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="2"/>
@@ -47884,7 +47893,7 @@
       <c r="Y661" s="2"/>
       <c r="Z661" s="2"/>
     </row>
-    <row r="662" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="2"/>
@@ -47912,7 +47921,7 @@
       <c r="Y662" s="2"/>
       <c r="Z662" s="2"/>
     </row>
-    <row r="663" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="2"/>
@@ -47940,7 +47949,7 @@
       <c r="Y663" s="2"/>
       <c r="Z663" s="2"/>
     </row>
-    <row r="664" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="2"/>
@@ -47968,7 +47977,7 @@
       <c r="Y664" s="2"/>
       <c r="Z664" s="2"/>
     </row>
-    <row r="665" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="2"/>
@@ -47996,7 +48005,7 @@
       <c r="Y665" s="2"/>
       <c r="Z665" s="2"/>
     </row>
-    <row r="666" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="2"/>
@@ -48024,7 +48033,7 @@
       <c r="Y666" s="2"/>
       <c r="Z666" s="2"/>
     </row>
-    <row r="667" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="2"/>
@@ -48052,7 +48061,7 @@
       <c r="Y667" s="2"/>
       <c r="Z667" s="2"/>
     </row>
-    <row r="668" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="2"/>
@@ -48080,7 +48089,7 @@
       <c r="Y668" s="2"/>
       <c r="Z668" s="2"/>
     </row>
-    <row r="669" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="2"/>
@@ -48108,7 +48117,7 @@
       <c r="Y669" s="2"/>
       <c r="Z669" s="2"/>
     </row>
-    <row r="670" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="2"/>
@@ -48136,7 +48145,7 @@
       <c r="Y670" s="2"/>
       <c r="Z670" s="2"/>
     </row>
-    <row r="671" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="2"/>
@@ -48164,7 +48173,7 @@
       <c r="Y671" s="2"/>
       <c r="Z671" s="2"/>
     </row>
-    <row r="672" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="2"/>
@@ -48192,7 +48201,7 @@
       <c r="Y672" s="2"/>
       <c r="Z672" s="2"/>
     </row>
-    <row r="673" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="2"/>
@@ -48220,7 +48229,7 @@
       <c r="Y673" s="2"/>
       <c r="Z673" s="2"/>
     </row>
-    <row r="674" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="2"/>
@@ -48248,7 +48257,7 @@
       <c r="Y674" s="2"/>
       <c r="Z674" s="2"/>
     </row>
-    <row r="675" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="2"/>
@@ -48276,7 +48285,7 @@
       <c r="Y675" s="2"/>
       <c r="Z675" s="2"/>
     </row>
-    <row r="676" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="2"/>
@@ -48304,7 +48313,7 @@
       <c r="Y676" s="2"/>
       <c r="Z676" s="2"/>
     </row>
-    <row r="677" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="2"/>
@@ -48332,7 +48341,7 @@
       <c r="Y677" s="2"/>
       <c r="Z677" s="2"/>
     </row>
-    <row r="678" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="2"/>
@@ -48360,7 +48369,7 @@
       <c r="Y678" s="2"/>
       <c r="Z678" s="2"/>
     </row>
-    <row r="679" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="2"/>
@@ -48388,7 +48397,7 @@
       <c r="Y679" s="2"/>
       <c r="Z679" s="2"/>
     </row>
-    <row r="680" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="2"/>
@@ -48416,7 +48425,7 @@
       <c r="Y680" s="2"/>
       <c r="Z680" s="2"/>
     </row>
-    <row r="681" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="2"/>
@@ -48444,7 +48453,7 @@
       <c r="Y681" s="2"/>
       <c r="Z681" s="2"/>
     </row>
-    <row r="682" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="2"/>
@@ -48472,7 +48481,7 @@
       <c r="Y682" s="2"/>
       <c r="Z682" s="2"/>
     </row>
-    <row r="683" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="2"/>
@@ -48500,7 +48509,7 @@
       <c r="Y683" s="2"/>
       <c r="Z683" s="2"/>
     </row>
-    <row r="684" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="2"/>
@@ -48528,7 +48537,7 @@
       <c r="Y684" s="2"/>
       <c r="Z684" s="2"/>
     </row>
-    <row r="685" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="2"/>
@@ -48556,7 +48565,7 @@
       <c r="Y685" s="2"/>
       <c r="Z685" s="2"/>
     </row>
-    <row r="686" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="2"/>
@@ -48584,7 +48593,7 @@
       <c r="Y686" s="2"/>
       <c r="Z686" s="2"/>
     </row>
-    <row r="687" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="2"/>
@@ -48612,7 +48621,7 @@
       <c r="Y687" s="2"/>
       <c r="Z687" s="2"/>
     </row>
-    <row r="688" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="2"/>
@@ -48640,7 +48649,7 @@
       <c r="Y688" s="2"/>
       <c r="Z688" s="2"/>
     </row>
-    <row r="689" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="2"/>
@@ -48668,7 +48677,7 @@
       <c r="Y689" s="2"/>
       <c r="Z689" s="2"/>
     </row>
-    <row r="690" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="2"/>
@@ -48696,7 +48705,7 @@
       <c r="Y690" s="2"/>
       <c r="Z690" s="2"/>
     </row>
-    <row r="691" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="2"/>
@@ -48724,7 +48733,7 @@
       <c r="Y691" s="2"/>
       <c r="Z691" s="2"/>
     </row>
-    <row r="692" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="2"/>
@@ -48752,7 +48761,7 @@
       <c r="Y692" s="2"/>
       <c r="Z692" s="2"/>
     </row>
-    <row r="693" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="2"/>
@@ -48780,7 +48789,7 @@
       <c r="Y693" s="2"/>
       <c r="Z693" s="2"/>
     </row>
-    <row r="694" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="2"/>
@@ -48808,7 +48817,7 @@
       <c r="Y694" s="2"/>
       <c r="Z694" s="2"/>
     </row>
-    <row r="695" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="2"/>
@@ -48836,7 +48845,7 @@
       <c r="Y695" s="2"/>
       <c r="Z695" s="2"/>
     </row>
-    <row r="696" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="2"/>
@@ -48864,7 +48873,7 @@
       <c r="Y696" s="2"/>
       <c r="Z696" s="2"/>
     </row>
-    <row r="697" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="2"/>
@@ -48892,7 +48901,7 @@
       <c r="Y697" s="2"/>
       <c r="Z697" s="2"/>
     </row>
-    <row r="698" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="2"/>
@@ -48920,7 +48929,7 @@
       <c r="Y698" s="2"/>
       <c r="Z698" s="2"/>
     </row>
-    <row r="699" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="2"/>
@@ -48948,7 +48957,7 @@
       <c r="Y699" s="2"/>
       <c r="Z699" s="2"/>
     </row>
-    <row r="700" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="2"/>
@@ -48976,7 +48985,7 @@
       <c r="Y700" s="2"/>
       <c r="Z700" s="2"/>
     </row>
-    <row r="701" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="2"/>
@@ -49004,7 +49013,7 @@
       <c r="Y701" s="2"/>
       <c r="Z701" s="2"/>
     </row>
-    <row r="702" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="2"/>
@@ -49032,7 +49041,7 @@
       <c r="Y702" s="2"/>
       <c r="Z702" s="2"/>
     </row>
-    <row r="703" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="2"/>
@@ -49060,7 +49069,7 @@
       <c r="Y703" s="2"/>
       <c r="Z703" s="2"/>
     </row>
-    <row r="704" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="2"/>
@@ -49088,7 +49097,7 @@
       <c r="Y704" s="2"/>
       <c r="Z704" s="2"/>
     </row>
-    <row r="705" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
@@ -49116,7 +49125,7 @@
       <c r="Y705" s="2"/>
       <c r="Z705" s="2"/>
     </row>
-    <row r="706" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="2"/>
@@ -49144,7 +49153,7 @@
       <c r="Y706" s="2"/>
       <c r="Z706" s="2"/>
     </row>
-    <row r="707" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="2"/>
@@ -49172,7 +49181,7 @@
       <c r="Y707" s="2"/>
       <c r="Z707" s="2"/>
     </row>
-    <row r="708" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="2"/>
@@ -49200,7 +49209,7 @@
       <c r="Y708" s="2"/>
       <c r="Z708" s="2"/>
     </row>
-    <row r="709" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="2"/>
@@ -49228,7 +49237,7 @@
       <c r="Y709" s="2"/>
       <c r="Z709" s="2"/>
     </row>
-    <row r="710" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="2"/>
@@ -49256,7 +49265,7 @@
       <c r="Y710" s="2"/>
       <c r="Z710" s="2"/>
     </row>
-    <row r="711" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="2"/>
@@ -49284,7 +49293,7 @@
       <c r="Y711" s="2"/>
       <c r="Z711" s="2"/>
     </row>
-    <row r="712" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="2"/>
@@ -49312,7 +49321,7 @@
       <c r="Y712" s="2"/>
       <c r="Z712" s="2"/>
     </row>
-    <row r="713" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="2"/>
@@ -49340,7 +49349,7 @@
       <c r="Y713" s="2"/>
       <c r="Z713" s="2"/>
     </row>
-    <row r="714" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="2"/>
@@ -49368,7 +49377,7 @@
       <c r="Y714" s="2"/>
       <c r="Z714" s="2"/>
     </row>
-    <row r="715" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
@@ -49396,7 +49405,7 @@
       <c r="Y715" s="2"/>
       <c r="Z715" s="2"/>
     </row>
-    <row r="716" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="2"/>
@@ -49424,7 +49433,7 @@
       <c r="Y716" s="2"/>
       <c r="Z716" s="2"/>
     </row>
-    <row r="717" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="2"/>
@@ -49452,7 +49461,7 @@
       <c r="Y717" s="2"/>
       <c r="Z717" s="2"/>
     </row>
-    <row r="718" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="2"/>
@@ -49480,7 +49489,7 @@
       <c r="Y718" s="2"/>
       <c r="Z718" s="2"/>
     </row>
-    <row r="719" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="2"/>
@@ -49508,7 +49517,7 @@
       <c r="Y719" s="2"/>
       <c r="Z719" s="2"/>
     </row>
-    <row r="720" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="2"/>
@@ -49536,7 +49545,7 @@
       <c r="Y720" s="2"/>
       <c r="Z720" s="2"/>
     </row>
-    <row r="721" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="2"/>
@@ -49564,7 +49573,7 @@
       <c r="Y721" s="2"/>
       <c r="Z721" s="2"/>
     </row>
-    <row r="722" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="2"/>
@@ -49592,7 +49601,7 @@
       <c r="Y722" s="2"/>
       <c r="Z722" s="2"/>
     </row>
-    <row r="723" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="2"/>
@@ -49620,7 +49629,7 @@
       <c r="Y723" s="2"/>
       <c r="Z723" s="2"/>
     </row>
-    <row r="724" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="2"/>
@@ -49648,7 +49657,7 @@
       <c r="Y724" s="2"/>
       <c r="Z724" s="2"/>
     </row>
-    <row r="725" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="2"/>
@@ -49676,7 +49685,7 @@
       <c r="Y725" s="2"/>
       <c r="Z725" s="2"/>
     </row>
-    <row r="726" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="2"/>
@@ -49704,7 +49713,7 @@
       <c r="Y726" s="2"/>
       <c r="Z726" s="2"/>
     </row>
-    <row r="727" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="2"/>
@@ -49732,7 +49741,7 @@
       <c r="Y727" s="2"/>
       <c r="Z727" s="2"/>
     </row>
-    <row r="728" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="2"/>
@@ -49760,7 +49769,7 @@
       <c r="Y728" s="2"/>
       <c r="Z728" s="2"/>
     </row>
-    <row r="729" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="2"/>
@@ -49788,7 +49797,7 @@
       <c r="Y729" s="2"/>
       <c r="Z729" s="2"/>
     </row>
-    <row r="730" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="2"/>
@@ -49816,7 +49825,7 @@
       <c r="Y730" s="2"/>
       <c r="Z730" s="2"/>
     </row>
-    <row r="731" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="2"/>
@@ -49844,7 +49853,7 @@
       <c r="Y731" s="2"/>
       <c r="Z731" s="2"/>
     </row>
-    <row r="732" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="2"/>
@@ -49872,7 +49881,7 @@
       <c r="Y732" s="2"/>
       <c r="Z732" s="2"/>
     </row>
-    <row r="733" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="2"/>
@@ -49900,7 +49909,7 @@
       <c r="Y733" s="2"/>
       <c r="Z733" s="2"/>
     </row>
-    <row r="734" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="2"/>
@@ -49928,7 +49937,7 @@
       <c r="Y734" s="2"/>
       <c r="Z734" s="2"/>
     </row>
-    <row r="735" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="2"/>
@@ -49956,7 +49965,7 @@
       <c r="Y735" s="2"/>
       <c r="Z735" s="2"/>
     </row>
-    <row r="736" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="2"/>
@@ -49984,7 +49993,7 @@
       <c r="Y736" s="2"/>
       <c r="Z736" s="2"/>
     </row>
-    <row r="737" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="2"/>
@@ -50012,7 +50021,7 @@
       <c r="Y737" s="2"/>
       <c r="Z737" s="2"/>
     </row>
-    <row r="738" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="2"/>
@@ -50040,7 +50049,7 @@
       <c r="Y738" s="2"/>
       <c r="Z738" s="2"/>
     </row>
-    <row r="739" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="2"/>
@@ -50068,7 +50077,7 @@
       <c r="Y739" s="2"/>
       <c r="Z739" s="2"/>
     </row>
-    <row r="740" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="2"/>
@@ -50096,7 +50105,7 @@
       <c r="Y740" s="2"/>
       <c r="Z740" s="2"/>
     </row>
-    <row r="741" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="2"/>
@@ -50124,7 +50133,7 @@
       <c r="Y741" s="2"/>
       <c r="Z741" s="2"/>
     </row>
-    <row r="742" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="2"/>
@@ -50152,7 +50161,7 @@
       <c r="Y742" s="2"/>
       <c r="Z742" s="2"/>
     </row>
-    <row r="743" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="2"/>
@@ -50180,7 +50189,7 @@
       <c r="Y743" s="2"/>
       <c r="Z743" s="2"/>
     </row>
-    <row r="744" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="2"/>
@@ -50208,7 +50217,7 @@
       <c r="Y744" s="2"/>
       <c r="Z744" s="2"/>
     </row>
-    <row r="745" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="2"/>
@@ -50236,7 +50245,7 @@
       <c r="Y745" s="2"/>
       <c r="Z745" s="2"/>
     </row>
-    <row r="746" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="2"/>
@@ -50264,7 +50273,7 @@
       <c r="Y746" s="2"/>
       <c r="Z746" s="2"/>
     </row>
-    <row r="747" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="2"/>
@@ -50292,7 +50301,7 @@
       <c r="Y747" s="2"/>
       <c r="Z747" s="2"/>
     </row>
-    <row r="748" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="2"/>
@@ -50320,7 +50329,7 @@
       <c r="Y748" s="2"/>
       <c r="Z748" s="2"/>
     </row>
-    <row r="749" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="2"/>
@@ -50348,7 +50357,7 @@
       <c r="Y749" s="2"/>
       <c r="Z749" s="2"/>
     </row>
-    <row r="750" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="2"/>
@@ -50376,7 +50385,7 @@
       <c r="Y750" s="2"/>
       <c r="Z750" s="2"/>
     </row>
-    <row r="751" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="2"/>
@@ -50404,7 +50413,7 @@
       <c r="Y751" s="2"/>
       <c r="Z751" s="2"/>
     </row>
-    <row r="752" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="2"/>
@@ -50432,7 +50441,7 @@
       <c r="Y752" s="2"/>
       <c r="Z752" s="2"/>
     </row>
-    <row r="753" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="2"/>
@@ -50460,7 +50469,7 @@
       <c r="Y753" s="2"/>
       <c r="Z753" s="2"/>
     </row>
-    <row r="754" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="2"/>
@@ -50488,7 +50497,7 @@
       <c r="Y754" s="2"/>
       <c r="Z754" s="2"/>
     </row>
-    <row r="755" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="2"/>
@@ -50516,7 +50525,7 @@
       <c r="Y755" s="2"/>
       <c r="Z755" s="2"/>
     </row>
-    <row r="756" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="2"/>
@@ -50544,7 +50553,7 @@
       <c r="Y756" s="2"/>
       <c r="Z756" s="2"/>
     </row>
-    <row r="757" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="2"/>
@@ -50572,7 +50581,7 @@
       <c r="Y757" s="2"/>
       <c r="Z757" s="2"/>
     </row>
-    <row r="758" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="2"/>
@@ -50600,7 +50609,7 @@
       <c r="Y758" s="2"/>
       <c r="Z758" s="2"/>
     </row>
-    <row r="759" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="2"/>
@@ -50628,7 +50637,7 @@
       <c r="Y759" s="2"/>
       <c r="Z759" s="2"/>
     </row>
-    <row r="760" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="2"/>
@@ -50656,7 +50665,7 @@
       <c r="Y760" s="2"/>
       <c r="Z760" s="2"/>
     </row>
-    <row r="761" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="2"/>
@@ -50684,7 +50693,7 @@
       <c r="Y761" s="2"/>
       <c r="Z761" s="2"/>
     </row>
-    <row r="762" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="2"/>
@@ -50712,7 +50721,7 @@
       <c r="Y762" s="2"/>
       <c r="Z762" s="2"/>
     </row>
-    <row r="763" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="2"/>
@@ -50740,7 +50749,7 @@
       <c r="Y763" s="2"/>
       <c r="Z763" s="2"/>
     </row>
-    <row r="764" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="2"/>
@@ -50768,7 +50777,7 @@
       <c r="Y764" s="2"/>
       <c r="Z764" s="2"/>
     </row>
-    <row r="765" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="2"/>
@@ -50796,7 +50805,7 @@
       <c r="Y765" s="2"/>
       <c r="Z765" s="2"/>
     </row>
-    <row r="766" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="2"/>
@@ -50824,7 +50833,7 @@
       <c r="Y766" s="2"/>
       <c r="Z766" s="2"/>
     </row>
-    <row r="767" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="2"/>
@@ -50852,7 +50861,7 @@
       <c r="Y767" s="2"/>
       <c r="Z767" s="2"/>
     </row>
-    <row r="768" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="2"/>
@@ -50880,7 +50889,7 @@
       <c r="Y768" s="2"/>
       <c r="Z768" s="2"/>
     </row>
-    <row r="769" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="2"/>
@@ -50908,7 +50917,7 @@
       <c r="Y769" s="2"/>
       <c r="Z769" s="2"/>
     </row>
-    <row r="770" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="2"/>
@@ -50936,7 +50945,7 @@
       <c r="Y770" s="2"/>
       <c r="Z770" s="2"/>
     </row>
-    <row r="771" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="2"/>
@@ -50964,7 +50973,7 @@
       <c r="Y771" s="2"/>
       <c r="Z771" s="2"/>
     </row>
-    <row r="772" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="2"/>
@@ -50992,7 +51001,7 @@
       <c r="Y772" s="2"/>
       <c r="Z772" s="2"/>
     </row>
-    <row r="773" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="2"/>
@@ -51020,7 +51029,7 @@
       <c r="Y773" s="2"/>
       <c r="Z773" s="2"/>
     </row>
-    <row r="774" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="2"/>
@@ -51048,7 +51057,7 @@
       <c r="Y774" s="2"/>
       <c r="Z774" s="2"/>
     </row>
-    <row r="775" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="2"/>
@@ -51076,7 +51085,7 @@
       <c r="Y775" s="2"/>
       <c r="Z775" s="2"/>
     </row>
-    <row r="776" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="2"/>
@@ -51104,7 +51113,7 @@
       <c r="Y776" s="2"/>
       <c r="Z776" s="2"/>
     </row>
-    <row r="777" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="2"/>
@@ -51132,7 +51141,7 @@
       <c r="Y777" s="2"/>
       <c r="Z777" s="2"/>
     </row>
-    <row r="778" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="2"/>
@@ -51160,7 +51169,7 @@
       <c r="Y778" s="2"/>
       <c r="Z778" s="2"/>
     </row>
-    <row r="779" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="2"/>
@@ -51188,7 +51197,7 @@
       <c r="Y779" s="2"/>
       <c r="Z779" s="2"/>
     </row>
-    <row r="780" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="2"/>
@@ -51216,7 +51225,7 @@
       <c r="Y780" s="2"/>
       <c r="Z780" s="2"/>
     </row>
-    <row r="781" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="2"/>
@@ -51244,7 +51253,7 @@
       <c r="Y781" s="2"/>
       <c r="Z781" s="2"/>
     </row>
-    <row r="782" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="2"/>
@@ -51272,7 +51281,7 @@
       <c r="Y782" s="2"/>
       <c r="Z782" s="2"/>
     </row>
-    <row r="783" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="2"/>
@@ -51300,7 +51309,7 @@
       <c r="Y783" s="2"/>
       <c r="Z783" s="2"/>
     </row>
-    <row r="784" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="2"/>
@@ -51328,7 +51337,7 @@
       <c r="Y784" s="2"/>
       <c r="Z784" s="2"/>
     </row>
-    <row r="785" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="2"/>
@@ -51356,7 +51365,7 @@
       <c r="Y785" s="2"/>
       <c r="Z785" s="2"/>
     </row>
-    <row r="786" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="2"/>
@@ -51384,7 +51393,7 @@
       <c r="Y786" s="2"/>
       <c r="Z786" s="2"/>
     </row>
-    <row r="787" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="2"/>
@@ -51412,7 +51421,7 @@
       <c r="Y787" s="2"/>
       <c r="Z787" s="2"/>
     </row>
-    <row r="788" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="2"/>
@@ -51440,7 +51449,7 @@
       <c r="Y788" s="2"/>
       <c r="Z788" s="2"/>
     </row>
-    <row r="789" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="2"/>
@@ -51468,7 +51477,7 @@
       <c r="Y789" s="2"/>
       <c r="Z789" s="2"/>
     </row>
-    <row r="790" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="2"/>
@@ -51496,7 +51505,7 @@
       <c r="Y790" s="2"/>
       <c r="Z790" s="2"/>
     </row>
-    <row r="791" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="2"/>
@@ -51524,7 +51533,7 @@
       <c r="Y791" s="2"/>
       <c r="Z791" s="2"/>
     </row>
-    <row r="792" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="2"/>
@@ -51552,7 +51561,7 @@
       <c r="Y792" s="2"/>
       <c r="Z792" s="2"/>
     </row>
-    <row r="793" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="2"/>
@@ -51580,7 +51589,7 @@
       <c r="Y793" s="2"/>
       <c r="Z793" s="2"/>
     </row>
-    <row r="794" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="2"/>
@@ -51608,7 +51617,7 @@
       <c r="Y794" s="2"/>
       <c r="Z794" s="2"/>
     </row>
-    <row r="795" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
@@ -51636,7 +51645,7 @@
       <c r="Y795" s="2"/>
       <c r="Z795" s="2"/>
     </row>
-    <row r="796" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="2"/>
@@ -51664,7 +51673,7 @@
       <c r="Y796" s="2"/>
       <c r="Z796" s="2"/>
     </row>
-    <row r="797" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="2"/>
@@ -51692,7 +51701,7 @@
       <c r="Y797" s="2"/>
       <c r="Z797" s="2"/>
     </row>
-    <row r="798" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="2"/>
@@ -51720,7 +51729,7 @@
       <c r="Y798" s="2"/>
       <c r="Z798" s="2"/>
     </row>
-    <row r="799" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="2"/>
@@ -51748,7 +51757,7 @@
       <c r="Y799" s="2"/>
       <c r="Z799" s="2"/>
     </row>
-    <row r="800" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="2"/>
@@ -51776,7 +51785,7 @@
       <c r="Y800" s="2"/>
       <c r="Z800" s="2"/>
     </row>
-    <row r="801" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="2"/>
@@ -51804,7 +51813,7 @@
       <c r="Y801" s="2"/>
       <c r="Z801" s="2"/>
     </row>
-    <row r="802" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="2"/>
@@ -51832,7 +51841,7 @@
       <c r="Y802" s="2"/>
       <c r="Z802" s="2"/>
     </row>
-    <row r="803" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="2"/>
@@ -51860,7 +51869,7 @@
       <c r="Y803" s="2"/>
       <c r="Z803" s="2"/>
     </row>
-    <row r="804" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="2"/>
@@ -51888,7 +51897,7 @@
       <c r="Y804" s="2"/>
       <c r="Z804" s="2"/>
     </row>
-    <row r="805" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="2"/>
@@ -51916,7 +51925,7 @@
       <c r="Y805" s="2"/>
       <c r="Z805" s="2"/>
     </row>
-    <row r="806" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="2"/>
@@ -51944,7 +51953,7 @@
       <c r="Y806" s="2"/>
       <c r="Z806" s="2"/>
     </row>
-    <row r="807" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="2"/>
@@ -51972,7 +51981,7 @@
       <c r="Y807" s="2"/>
       <c r="Z807" s="2"/>
     </row>
-    <row r="808" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="2"/>
@@ -52000,7 +52009,7 @@
       <c r="Y808" s="2"/>
       <c r="Z808" s="2"/>
     </row>
-    <row r="809" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="2"/>
@@ -52028,7 +52037,7 @@
       <c r="Y809" s="2"/>
       <c r="Z809" s="2"/>
     </row>
-    <row r="810" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="2"/>
@@ -52056,7 +52065,7 @@
       <c r="Y810" s="2"/>
       <c r="Z810" s="2"/>
     </row>
-    <row r="811" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="2"/>
@@ -52084,7 +52093,7 @@
       <c r="Y811" s="2"/>
       <c r="Z811" s="2"/>
     </row>
-    <row r="812" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="2"/>
@@ -52112,7 +52121,7 @@
       <c r="Y812" s="2"/>
       <c r="Z812" s="2"/>
     </row>
-    <row r="813" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="2"/>
@@ -52140,7 +52149,7 @@
       <c r="Y813" s="2"/>
       <c r="Z813" s="2"/>
     </row>
-    <row r="814" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="2"/>
@@ -52168,7 +52177,7 @@
       <c r="Y814" s="2"/>
       <c r="Z814" s="2"/>
     </row>
-    <row r="815" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="2"/>
@@ -52196,7 +52205,7 @@
       <c r="Y815" s="2"/>
       <c r="Z815" s="2"/>
     </row>
-    <row r="816" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="2"/>
@@ -52224,7 +52233,7 @@
       <c r="Y816" s="2"/>
       <c r="Z816" s="2"/>
     </row>
-    <row r="817" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="2"/>
@@ -52252,7 +52261,7 @@
       <c r="Y817" s="2"/>
       <c r="Z817" s="2"/>
     </row>
-    <row r="818" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="2"/>
@@ -52280,7 +52289,7 @@
       <c r="Y818" s="2"/>
       <c r="Z818" s="2"/>
     </row>
-    <row r="819" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="2"/>
@@ -52308,7 +52317,7 @@
       <c r="Y819" s="2"/>
       <c r="Z819" s="2"/>
     </row>
-    <row r="820" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="2"/>
@@ -52336,7 +52345,7 @@
       <c r="Y820" s="2"/>
       <c r="Z820" s="2"/>
     </row>
-    <row r="821" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="2"/>
@@ -52364,7 +52373,7 @@
       <c r="Y821" s="2"/>
       <c r="Z821" s="2"/>
     </row>
-    <row r="822" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="2"/>
@@ -52392,7 +52401,7 @@
       <c r="Y822" s="2"/>
       <c r="Z822" s="2"/>
     </row>
-    <row r="823" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="2"/>
@@ -52420,7 +52429,7 @@
       <c r="Y823" s="2"/>
       <c r="Z823" s="2"/>
     </row>
-    <row r="824" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="2"/>
@@ -52448,7 +52457,7 @@
       <c r="Y824" s="2"/>
       <c r="Z824" s="2"/>
     </row>
-    <row r="825" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="2"/>
@@ -52476,7 +52485,7 @@
       <c r="Y825" s="2"/>
       <c r="Z825" s="2"/>
     </row>
-    <row r="826" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="2"/>
@@ -52504,7 +52513,7 @@
       <c r="Y826" s="2"/>
       <c r="Z826" s="2"/>
     </row>
-    <row r="827" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="2"/>
@@ -52532,7 +52541,7 @@
       <c r="Y827" s="2"/>
       <c r="Z827" s="2"/>
     </row>
-    <row r="828" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="2"/>
@@ -52560,7 +52569,7 @@
       <c r="Y828" s="2"/>
       <c r="Z828" s="2"/>
     </row>
-    <row r="829" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="2"/>
@@ -52588,7 +52597,7 @@
       <c r="Y829" s="2"/>
       <c r="Z829" s="2"/>
     </row>
-    <row r="830" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="2"/>
@@ -52616,7 +52625,7 @@
       <c r="Y830" s="2"/>
       <c r="Z830" s="2"/>
     </row>
-    <row r="831" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="2"/>
@@ -52644,7 +52653,7 @@
       <c r="Y831" s="2"/>
       <c r="Z831" s="2"/>
     </row>
-    <row r="832" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="2"/>
@@ -52672,7 +52681,7 @@
       <c r="Y832" s="2"/>
       <c r="Z832" s="2"/>
     </row>
-    <row r="833" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="2"/>
@@ -52700,7 +52709,7 @@
       <c r="Y833" s="2"/>
       <c r="Z833" s="2"/>
     </row>
-    <row r="834" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="2"/>
@@ -52728,7 +52737,7 @@
       <c r="Y834" s="2"/>
       <c r="Z834" s="2"/>
     </row>
-    <row r="835" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="2"/>
@@ -52756,7 +52765,7 @@
       <c r="Y835" s="2"/>
       <c r="Z835" s="2"/>
     </row>
-    <row r="836" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="2"/>
@@ -52784,7 +52793,7 @@
       <c r="Y836" s="2"/>
       <c r="Z836" s="2"/>
     </row>
-    <row r="837" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="2"/>
@@ -52812,7 +52821,7 @@
       <c r="Y837" s="2"/>
       <c r="Z837" s="2"/>
     </row>
-    <row r="838" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="2"/>
@@ -52840,7 +52849,7 @@
       <c r="Y838" s="2"/>
       <c r="Z838" s="2"/>
     </row>
-    <row r="839" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="2"/>
@@ -52868,7 +52877,7 @@
       <c r="Y839" s="2"/>
       <c r="Z839" s="2"/>
     </row>
-    <row r="840" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="2"/>
@@ -52896,7 +52905,7 @@
       <c r="Y840" s="2"/>
       <c r="Z840" s="2"/>
     </row>
-    <row r="841" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="2"/>
@@ -52924,7 +52933,7 @@
       <c r="Y841" s="2"/>
       <c r="Z841" s="2"/>
     </row>
-    <row r="842" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="2"/>
@@ -52952,7 +52961,7 @@
       <c r="Y842" s="2"/>
       <c r="Z842" s="2"/>
     </row>
-    <row r="843" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="2"/>
@@ -52980,7 +52989,7 @@
       <c r="Y843" s="2"/>
       <c r="Z843" s="2"/>
     </row>
-    <row r="844" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="2"/>
@@ -53008,7 +53017,7 @@
       <c r="Y844" s="2"/>
       <c r="Z844" s="2"/>
     </row>
-    <row r="845" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="2"/>
@@ -53036,7 +53045,7 @@
       <c r="Y845" s="2"/>
       <c r="Z845" s="2"/>
     </row>
-    <row r="846" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="2"/>
@@ -53064,7 +53073,7 @@
       <c r="Y846" s="2"/>
       <c r="Z846" s="2"/>
     </row>
-    <row r="847" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="2"/>
@@ -53092,7 +53101,7 @@
       <c r="Y847" s="2"/>
       <c r="Z847" s="2"/>
     </row>
-    <row r="848" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="2"/>
@@ -53120,7 +53129,7 @@
       <c r="Y848" s="2"/>
       <c r="Z848" s="2"/>
     </row>
-    <row r="849" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="2"/>
@@ -53148,7 +53157,7 @@
       <c r="Y849" s="2"/>
       <c r="Z849" s="2"/>
     </row>
-    <row r="850" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="2"/>
@@ -53176,7 +53185,7 @@
       <c r="Y850" s="2"/>
       <c r="Z850" s="2"/>
     </row>
-    <row r="851" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="2"/>
@@ -53204,7 +53213,7 @@
       <c r="Y851" s="2"/>
       <c r="Z851" s="2"/>
     </row>
-    <row r="852" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="2"/>
@@ -53232,7 +53241,7 @@
       <c r="Y852" s="2"/>
       <c r="Z852" s="2"/>
     </row>
-    <row r="853" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="2"/>
@@ -53260,7 +53269,7 @@
       <c r="Y853" s="2"/>
       <c r="Z853" s="2"/>
     </row>
-    <row r="854" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="2"/>
@@ -53288,7 +53297,7 @@
       <c r="Y854" s="2"/>
       <c r="Z854" s="2"/>
     </row>
-    <row r="855" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="2"/>
@@ -53316,7 +53325,7 @@
       <c r="Y855" s="2"/>
       <c r="Z855" s="2"/>
     </row>
-    <row r="856" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="2"/>
@@ -53344,7 +53353,7 @@
       <c r="Y856" s="2"/>
       <c r="Z856" s="2"/>
     </row>
-    <row r="857" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="2"/>
@@ -53372,7 +53381,7 @@
       <c r="Y857" s="2"/>
       <c r="Z857" s="2"/>
     </row>
-    <row r="858" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="2"/>
@@ -53400,7 +53409,7 @@
       <c r="Y858" s="2"/>
       <c r="Z858" s="2"/>
     </row>
-    <row r="859" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="2"/>
@@ -53428,7 +53437,7 @@
       <c r="Y859" s="2"/>
       <c r="Z859" s="2"/>
     </row>
-    <row r="860" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="2"/>
@@ -53456,7 +53465,7 @@
       <c r="Y860" s="2"/>
       <c r="Z860" s="2"/>
     </row>
-    <row r="861" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="2"/>
@@ -53484,7 +53493,7 @@
       <c r="Y861" s="2"/>
       <c r="Z861" s="2"/>
     </row>
-    <row r="862" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="2"/>
@@ -53512,7 +53521,7 @@
       <c r="Y862" s="2"/>
       <c r="Z862" s="2"/>
     </row>
-    <row r="863" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="2"/>
@@ -53540,7 +53549,7 @@
       <c r="Y863" s="2"/>
       <c r="Z863" s="2"/>
     </row>
-    <row r="864" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="2"/>
@@ -53568,7 +53577,7 @@
       <c r="Y864" s="2"/>
       <c r="Z864" s="2"/>
     </row>
-    <row r="865" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="2"/>
@@ -53596,7 +53605,7 @@
       <c r="Y865" s="2"/>
       <c r="Z865" s="2"/>
     </row>
-    <row r="866" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="2"/>
@@ -53624,7 +53633,7 @@
       <c r="Y866" s="2"/>
       <c r="Z866" s="2"/>
     </row>
-    <row r="867" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="2"/>
@@ -53652,7 +53661,7 @@
       <c r="Y867" s="2"/>
       <c r="Z867" s="2"/>
     </row>
-    <row r="868" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="2"/>
@@ -53680,7 +53689,7 @@
       <c r="Y868" s="2"/>
       <c r="Z868" s="2"/>
     </row>
-    <row r="869" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="2"/>
@@ -53708,7 +53717,7 @@
       <c r="Y869" s="2"/>
       <c r="Z869" s="2"/>
     </row>
-    <row r="870" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="2"/>
@@ -53736,7 +53745,7 @@
       <c r="Y870" s="2"/>
       <c r="Z870" s="2"/>
     </row>
-    <row r="871" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="2"/>
@@ -53764,7 +53773,7 @@
       <c r="Y871" s="2"/>
       <c r="Z871" s="2"/>
     </row>
-    <row r="872" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="2"/>
@@ -53792,7 +53801,7 @@
       <c r="Y872" s="2"/>
       <c r="Z872" s="2"/>
     </row>
-    <row r="873" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="2"/>
@@ -53820,7 +53829,7 @@
       <c r="Y873" s="2"/>
       <c r="Z873" s="2"/>
     </row>
-    <row r="874" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="2"/>
@@ -53848,7 +53857,7 @@
       <c r="Y874" s="2"/>
       <c r="Z874" s="2"/>
     </row>
-    <row r="875" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="2"/>
@@ -53876,7 +53885,7 @@
       <c r="Y875" s="2"/>
       <c r="Z875" s="2"/>
     </row>
-    <row r="876" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="2"/>
@@ -53904,7 +53913,7 @@
       <c r="Y876" s="2"/>
       <c r="Z876" s="2"/>
     </row>
-    <row r="877" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="2"/>
@@ -53932,7 +53941,7 @@
       <c r="Y877" s="2"/>
       <c r="Z877" s="2"/>
     </row>
-    <row r="878" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="2"/>
@@ -53960,7 +53969,7 @@
       <c r="Y878" s="2"/>
       <c r="Z878" s="2"/>
     </row>
-    <row r="879" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="2"/>
@@ -53988,7 +53997,7 @@
       <c r="Y879" s="2"/>
       <c r="Z879" s="2"/>
     </row>
-    <row r="880" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="2"/>
@@ -54016,7 +54025,7 @@
       <c r="Y880" s="2"/>
       <c r="Z880" s="2"/>
     </row>
-    <row r="881" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="2"/>
@@ -54044,7 +54053,7 @@
       <c r="Y881" s="2"/>
       <c r="Z881" s="2"/>
     </row>
-    <row r="882" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="2"/>
@@ -54072,7 +54081,7 @@
       <c r="Y882" s="2"/>
       <c r="Z882" s="2"/>
     </row>
-    <row r="883" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="2"/>
@@ -54100,7 +54109,7 @@
       <c r="Y883" s="2"/>
       <c r="Z883" s="2"/>
     </row>
-    <row r="884" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="2"/>
@@ -54128,7 +54137,7 @@
       <c r="Y884" s="2"/>
       <c r="Z884" s="2"/>
     </row>
-    <row r="885" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="2"/>
@@ -54156,7 +54165,7 @@
       <c r="Y885" s="2"/>
       <c r="Z885" s="2"/>
     </row>
-    <row r="886" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="2"/>
@@ -54184,7 +54193,7 @@
       <c r="Y886" s="2"/>
       <c r="Z886" s="2"/>
     </row>
-    <row r="887" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="2"/>
@@ -54212,7 +54221,7 @@
       <c r="Y887" s="2"/>
       <c r="Z887" s="2"/>
     </row>
-    <row r="888" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="2"/>
@@ -54240,7 +54249,7 @@
       <c r="Y888" s="2"/>
       <c r="Z888" s="2"/>
     </row>
-    <row r="889" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="2"/>
@@ -54268,7 +54277,7 @@
       <c r="Y889" s="2"/>
       <c r="Z889" s="2"/>
     </row>
-    <row r="890" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="2"/>
@@ -54296,7 +54305,7 @@
       <c r="Y890" s="2"/>
       <c r="Z890" s="2"/>
     </row>
-    <row r="891" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="2"/>
@@ -54324,7 +54333,7 @@
       <c r="Y891" s="2"/>
       <c r="Z891" s="2"/>
     </row>
-    <row r="892" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="2"/>
@@ -54352,7 +54361,7 @@
       <c r="Y892" s="2"/>
       <c r="Z892" s="2"/>
     </row>
-    <row r="893" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="2"/>
@@ -54380,7 +54389,7 @@
       <c r="Y893" s="2"/>
       <c r="Z893" s="2"/>
     </row>
-    <row r="894" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="2"/>
@@ -54408,7 +54417,7 @@
       <c r="Y894" s="2"/>
       <c r="Z894" s="2"/>
     </row>
-    <row r="895" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="2"/>
@@ -54436,7 +54445,7 @@
       <c r="Y895" s="2"/>
       <c r="Z895" s="2"/>
     </row>
-    <row r="896" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="2"/>
@@ -54464,7 +54473,7 @@
       <c r="Y896" s="2"/>
       <c r="Z896" s="2"/>
     </row>
-    <row r="897" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="2"/>
@@ -54492,7 +54501,7 @@
       <c r="Y897" s="2"/>
       <c r="Z897" s="2"/>
     </row>
-    <row r="898" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="2"/>
@@ -54520,7 +54529,7 @@
       <c r="Y898" s="2"/>
       <c r="Z898" s="2"/>
     </row>
-    <row r="899" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="2"/>
@@ -54548,7 +54557,7 @@
       <c r="Y899" s="2"/>
       <c r="Z899" s="2"/>
     </row>
-    <row r="900" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="2"/>
@@ -54576,7 +54585,7 @@
       <c r="Y900" s="2"/>
       <c r="Z900" s="2"/>
     </row>
-    <row r="901" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="2"/>
@@ -54604,7 +54613,7 @@
       <c r="Y901" s="2"/>
       <c r="Z901" s="2"/>
     </row>
-    <row r="902" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="2"/>
@@ -54632,7 +54641,7 @@
       <c r="Y902" s="2"/>
       <c r="Z902" s="2"/>
     </row>
-    <row r="903" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="2"/>
@@ -54660,7 +54669,7 @@
       <c r="Y903" s="2"/>
       <c r="Z903" s="2"/>
     </row>
-    <row r="904" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="2"/>
@@ -54688,7 +54697,7 @@
       <c r="Y904" s="2"/>
       <c r="Z904" s="2"/>
     </row>
-    <row r="905" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="2"/>
@@ -54716,7 +54725,7 @@
       <c r="Y905" s="2"/>
       <c r="Z905" s="2"/>
     </row>
-    <row r="906" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="2"/>
@@ -54744,7 +54753,7 @@
       <c r="Y906" s="2"/>
       <c r="Z906" s="2"/>
     </row>
-    <row r="907" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="2"/>
@@ -54772,7 +54781,7 @@
       <c r="Y907" s="2"/>
       <c r="Z907" s="2"/>
     </row>
-    <row r="908" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="2"/>
@@ -54800,7 +54809,7 @@
       <c r="Y908" s="2"/>
       <c r="Z908" s="2"/>
     </row>
-    <row r="909" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="2"/>
@@ -54828,7 +54837,7 @@
       <c r="Y909" s="2"/>
       <c r="Z909" s="2"/>
     </row>
-    <row r="910" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="2"/>
@@ -54856,7 +54865,7 @@
       <c r="Y910" s="2"/>
       <c r="Z910" s="2"/>
     </row>
-    <row r="911" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="2"/>
@@ -54884,7 +54893,7 @@
       <c r="Y911" s="2"/>
       <c r="Z911" s="2"/>
     </row>
-    <row r="912" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="2"/>
@@ -54912,7 +54921,7 @@
       <c r="Y912" s="2"/>
       <c r="Z912" s="2"/>
     </row>
-    <row r="913" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="2"/>
@@ -54940,7 +54949,7 @@
       <c r="Y913" s="2"/>
       <c r="Z913" s="2"/>
     </row>
-    <row r="914" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="2"/>
@@ -54968,7 +54977,7 @@
       <c r="Y914" s="2"/>
       <c r="Z914" s="2"/>
     </row>
-    <row r="915" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="2"/>
@@ -54996,7 +55005,7 @@
       <c r="Y915" s="2"/>
       <c r="Z915" s="2"/>
     </row>
-    <row r="916" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="2"/>
@@ -55024,7 +55033,7 @@
       <c r="Y916" s="2"/>
       <c r="Z916" s="2"/>
     </row>
-    <row r="917" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="2"/>
@@ -55052,7 +55061,7 @@
       <c r="Y917" s="2"/>
       <c r="Z917" s="2"/>
     </row>
-    <row r="918" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="2"/>
@@ -55080,7 +55089,7 @@
       <c r="Y918" s="2"/>
       <c r="Z918" s="2"/>
     </row>
-    <row r="919" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="2"/>
@@ -55108,7 +55117,7 @@
       <c r="Y919" s="2"/>
       <c r="Z919" s="2"/>
     </row>
-    <row r="920" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="2"/>
@@ -55136,7 +55145,7 @@
       <c r="Y920" s="2"/>
       <c r="Z920" s="2"/>
     </row>
-    <row r="921" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="2"/>
@@ -55164,7 +55173,7 @@
       <c r="Y921" s="2"/>
       <c r="Z921" s="2"/>
     </row>
-    <row r="922" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="2"/>
@@ -55192,7 +55201,7 @@
       <c r="Y922" s="2"/>
       <c r="Z922" s="2"/>
     </row>
-    <row r="923" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="2"/>
@@ -55220,7 +55229,7 @@
       <c r="Y923" s="2"/>
       <c r="Z923" s="2"/>
     </row>
-    <row r="924" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="2"/>
@@ -55248,7 +55257,7 @@
       <c r="Y924" s="2"/>
       <c r="Z924" s="2"/>
     </row>
-    <row r="925" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="2"/>
@@ -55276,7 +55285,7 @@
       <c r="Y925" s="2"/>
       <c r="Z925" s="2"/>
     </row>
-    <row r="926" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="2"/>
@@ -55304,7 +55313,7 @@
       <c r="Y926" s="2"/>
       <c r="Z926" s="2"/>
     </row>
-    <row r="927" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="2"/>
@@ -55332,7 +55341,7 @@
       <c r="Y927" s="2"/>
       <c r="Z927" s="2"/>
     </row>
-    <row r="928" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="2"/>
@@ -55360,7 +55369,7 @@
       <c r="Y928" s="2"/>
       <c r="Z928" s="2"/>
     </row>
-    <row r="929" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="2"/>
@@ -55388,7 +55397,7 @@
       <c r="Y929" s="2"/>
       <c r="Z929" s="2"/>
     </row>
-    <row r="930" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="2"/>
@@ -55416,7 +55425,7 @@
       <c r="Y930" s="2"/>
       <c r="Z930" s="2"/>
     </row>
-    <row r="931" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="2"/>
@@ -55444,7 +55453,7 @@
       <c r="Y931" s="2"/>
       <c r="Z931" s="2"/>
     </row>
-    <row r="932" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="2"/>
@@ -55472,7 +55481,7 @@
       <c r="Y932" s="2"/>
       <c r="Z932" s="2"/>
     </row>
-    <row r="933" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="2"/>
@@ -55500,7 +55509,7 @@
       <c r="Y933" s="2"/>
       <c r="Z933" s="2"/>
     </row>
-    <row r="934" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="2"/>
@@ -55528,7 +55537,7 @@
       <c r="Y934" s="2"/>
       <c r="Z934" s="2"/>
     </row>
-    <row r="935" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="2"/>
@@ -55556,7 +55565,7 @@
       <c r="Y935" s="2"/>
       <c r="Z935" s="2"/>
     </row>
-    <row r="936" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="2"/>
@@ -55584,7 +55593,7 @@
       <c r="Y936" s="2"/>
       <c r="Z936" s="2"/>
     </row>
-    <row r="937" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="2"/>
@@ -55612,7 +55621,7 @@
       <c r="Y937" s="2"/>
       <c r="Z937" s="2"/>
     </row>
-    <row r="938" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="2"/>
@@ -55640,7 +55649,7 @@
       <c r="Y938" s="2"/>
       <c r="Z938" s="2"/>
     </row>
-    <row r="939" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="2"/>
@@ -55668,7 +55677,7 @@
       <c r="Y939" s="2"/>
       <c r="Z939" s="2"/>
     </row>
-    <row r="940" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="2"/>
@@ -55696,7 +55705,7 @@
       <c r="Y940" s="2"/>
       <c r="Z940" s="2"/>
     </row>
-    <row r="941" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="2"/>
@@ -55724,7 +55733,7 @@
       <c r="Y941" s="2"/>
       <c r="Z941" s="2"/>
     </row>
-    <row r="942" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="2"/>
@@ -55752,7 +55761,7 @@
       <c r="Y942" s="2"/>
       <c r="Z942" s="2"/>
     </row>
-    <row r="943" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="2"/>
@@ -55780,7 +55789,7 @@
       <c r="Y943" s="2"/>
       <c r="Z943" s="2"/>
     </row>
-    <row r="944" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="2"/>
@@ -55808,7 +55817,7 @@
       <c r="Y944" s="2"/>
       <c r="Z944" s="2"/>
     </row>
-    <row r="945" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="2"/>
@@ -55836,7 +55845,7 @@
       <c r="Y945" s="2"/>
       <c r="Z945" s="2"/>
     </row>
-    <row r="946" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="2"/>
@@ -55864,7 +55873,7 @@
       <c r="Y946" s="2"/>
       <c r="Z946" s="2"/>
     </row>
-    <row r="947" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="2"/>
@@ -55892,7 +55901,7 @@
       <c r="Y947" s="2"/>
       <c r="Z947" s="2"/>
     </row>
-    <row r="948" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="2"/>
@@ -55920,7 +55929,7 @@
       <c r="Y948" s="2"/>
       <c r="Z948" s="2"/>
     </row>
-    <row r="949" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="2"/>
@@ -55948,7 +55957,7 @@
       <c r="Y949" s="2"/>
       <c r="Z949" s="2"/>
     </row>
-    <row r="950" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="2"/>
@@ -55976,7 +55985,7 @@
       <c r="Y950" s="2"/>
       <c r="Z950" s="2"/>
     </row>
-    <row r="951" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="2"/>
